--- a/docs/v2/MacaulayDuration_计量模版.xlsx
+++ b/docs/v2/MacaulayDuration_计量模版.xlsx
@@ -8422,7 +8422,7 @@
         </is>
       </c>
       <c r="B15" s="57">
-        <f>TEXT(-'麦考林久期计算表'!$G$33*0.025*100,"+0.0000")&amp;"% ("&amp;IF(-'麦考林久期计算表'!$G$33&gt;0,"NII 受损","NII 受益")&amp;")"</f>
+        <f>TEXT(ABS('麦考林久期计算表'!$G$33*0.025*100),"0.0000")&amp;"% ("&amp;IF('麦考林久期计算表'!$G$33&gt;0,"NII 受损","NII 受益")&amp;")"</f>
         <v/>
       </c>
       <c r="C15" s="58" t="n"/>
@@ -8438,7 +8438,7 @@
         </is>
       </c>
       <c r="B16" s="57">
-        <f>TEXT('麦考林久期计算表'!$G$33*0.025*100,"+0.0000")&amp;"% ("&amp;IF('麦考林久期计算表'!$G$33&gt;0,"NII 受损","NII 受益")&amp;")"</f>
+        <f>TEXT(ABS('麦考林久期计算表'!$G$33*0.025*100),"0.0000")&amp;"% ("&amp;IF('麦考林久期计算表'!$G$33&gt;0,"NII 受损","NII 受益")&amp;")"</f>
         <v/>
       </c>
       <c r="C16" s="58" t="n"/>
@@ -8589,11 +8589,11 @@
         <v/>
       </c>
       <c r="E5" s="29">
-        <f>SUMPRODUCT(折现数据源!E$4:E$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!F$4:F$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!G$4:G$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!H$4:H$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!I$4:I$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!J$4:J$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!K$4:K$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!L$4:L$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!M$4:M$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!N$4:N$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!O$4:O$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!P$4:P$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Q$4:Q$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!R$4:R$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!S$4:S$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!T$4:T$67,折现数据源!$D$4:$D$67)</f>
+        <f>折现数据源!E4*折现数据源!$D$4+折现数据源!F4*折现数据源!$D$4+折现数据源!G4*折现数据源!$D$4+折现数据源!H4*折现数据源!$D$4+折现数据源!I4*折现数据源!$D$4+折现数据源!J4*折现数据源!$D$4+折现数据源!K4*折现数据源!$D$4+折现数据源!L4*折现数据源!$D$4+折现数据源!M4*折现数据源!$D$4+折现数据源!N4*折现数据源!$D$4+折现数据源!O4*折现数据源!$D$4+折现数据源!P4*折现数据源!$D$4+折现数据源!Q4*折现数据源!$D$4+折现数据源!R4*折现数据源!$D$4+折现数据源!S4*折现数据源!$D$4+折现数据源!T4*折现数据源!$D$4</f>
         <v/>
       </c>
       <c r="F5" s="29">
-        <f>SUMPRODUCT(折现数据源!U$4:U$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!V$4:V$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!W$4:W$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!X$4:X$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Y$4:Y$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Z$4:Z$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!AA$4:AA$67,折现数据源!$D$4:$D$67)</f>
+        <f>折现数据源!U4*折现数据源!$D$4+折现数据源!V4*折现数据源!$D$4+折现数据源!W4*折现数据源!$D$4+折现数据源!X4*折现数据源!$D$4+折现数据源!Y4*折现数据源!$D$4+折现数据源!Z4*折现数据源!$D$4+折现数据源!AA4*折现数据源!$D$4</f>
         <v/>
       </c>
       <c r="G5" s="31">
@@ -8623,11 +8623,11 @@
         <v/>
       </c>
       <c r="E6" s="29">
-        <f>SUMPRODUCT(折现数据源!E$4:E$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!F$4:F$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!G$4:G$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!H$4:H$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!I$4:I$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!J$4:J$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!K$4:K$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!L$4:L$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!M$4:M$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!N$4:N$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!O$4:O$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!P$4:P$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Q$4:Q$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!R$4:R$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!S$4:S$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!T$4:T$67,折现数据源!$D$4:$D$67)</f>
+        <f>折现数据源!E5*折现数据源!$D$5+折现数据源!F5*折现数据源!$D$5+折现数据源!G5*折现数据源!$D$5+折现数据源!H5*折现数据源!$D$5+折现数据源!I5*折现数据源!$D$5+折现数据源!J5*折现数据源!$D$5+折现数据源!K5*折现数据源!$D$5+折现数据源!L5*折现数据源!$D$5+折现数据源!M5*折现数据源!$D$5+折现数据源!N5*折现数据源!$D$5+折现数据源!O5*折现数据源!$D$5+折现数据源!P5*折现数据源!$D$5+折现数据源!Q5*折现数据源!$D$5+折现数据源!R5*折现数据源!$D$5+折现数据源!S5*折现数据源!$D$5+折现数据源!T5*折现数据源!$D$5</f>
         <v/>
       </c>
       <c r="F6" s="29">
-        <f>SUMPRODUCT(折现数据源!U$4:U$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!V$4:V$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!W$4:W$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!X$4:X$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Y$4:Y$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Z$4:Z$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!AA$4:AA$67,折现数据源!$D$4:$D$67)</f>
+        <f>折现数据源!U5*折现数据源!$D$5+折现数据源!V5*折现数据源!$D$5+折现数据源!W5*折现数据源!$D$5+折现数据源!X5*折现数据源!$D$5+折现数据源!Y5*折现数据源!$D$5+折现数据源!Z5*折现数据源!$D$5+折现数据源!AA5*折现数据源!$D$5</f>
         <v/>
       </c>
       <c r="G6" s="31">
@@ -8657,11 +8657,11 @@
         <v/>
       </c>
       <c r="E7" s="29">
-        <f>SUMPRODUCT(折现数据源!E$4:E$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!F$4:F$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!G$4:G$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!H$4:H$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!I$4:I$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!J$4:J$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!K$4:K$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!L$4:L$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!M$4:M$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!N$4:N$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!O$4:O$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!P$4:P$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Q$4:Q$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!R$4:R$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!S$4:S$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!T$4:T$67,折现数据源!$D$4:$D$67)</f>
+        <f>折现数据源!E6*折现数据源!$D$6+折现数据源!F6*折现数据源!$D$6+折现数据源!G6*折现数据源!$D$6+折现数据源!H6*折现数据源!$D$6+折现数据源!I6*折现数据源!$D$6+折现数据源!J6*折现数据源!$D$6+折现数据源!K6*折现数据源!$D$6+折现数据源!L6*折现数据源!$D$6+折现数据源!M6*折现数据源!$D$6+折现数据源!N6*折现数据源!$D$6+折现数据源!O6*折现数据源!$D$6+折现数据源!P6*折现数据源!$D$6+折现数据源!Q6*折现数据源!$D$6+折现数据源!R6*折现数据源!$D$6+折现数据源!S6*折现数据源!$D$6+折现数据源!T6*折现数据源!$D$6</f>
         <v/>
       </c>
       <c r="F7" s="29">
-        <f>SUMPRODUCT(折现数据源!U$4:U$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!V$4:V$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!W$4:W$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!X$4:X$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Y$4:Y$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Z$4:Z$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!AA$4:AA$67,折现数据源!$D$4:$D$67)</f>
+        <f>折现数据源!U6*折现数据源!$D$6+折现数据源!V6*折现数据源!$D$6+折现数据源!W6*折现数据源!$D$6+折现数据源!X6*折现数据源!$D$6+折现数据源!Y6*折现数据源!$D$6+折现数据源!Z6*折现数据源!$D$6+折现数据源!AA6*折现数据源!$D$6</f>
         <v/>
       </c>
       <c r="G7" s="31">
@@ -8691,11 +8691,11 @@
         <v/>
       </c>
       <c r="E8" s="29">
-        <f>SUMPRODUCT(折现数据源!E$4:E$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!F$4:F$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!G$4:G$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!H$4:H$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!I$4:I$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!J$4:J$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!K$4:K$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!L$4:L$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!M$4:M$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!N$4:N$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!O$4:O$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!P$4:P$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Q$4:Q$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!R$4:R$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!S$4:S$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!T$4:T$67,折现数据源!$D$4:$D$67)</f>
+        <f>折现数据源!E7*折现数据源!$D$7+折现数据源!F7*折现数据源!$D$7+折现数据源!G7*折现数据源!$D$7+折现数据源!H7*折现数据源!$D$7+折现数据源!I7*折现数据源!$D$7+折现数据源!J7*折现数据源!$D$7+折现数据源!K7*折现数据源!$D$7+折现数据源!L7*折现数据源!$D$7+折现数据源!M7*折现数据源!$D$7+折现数据源!N7*折现数据源!$D$7+折现数据源!O7*折现数据源!$D$7+折现数据源!P7*折现数据源!$D$7+折现数据源!Q7*折现数据源!$D$7+折现数据源!R7*折现数据源!$D$7+折现数据源!S7*折现数据源!$D$7+折现数据源!T7*折现数据源!$D$7</f>
         <v/>
       </c>
       <c r="F8" s="29">
-        <f>SUMPRODUCT(折现数据源!U$4:U$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!V$4:V$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!W$4:W$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!X$4:X$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Y$4:Y$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Z$4:Z$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!AA$4:AA$67,折现数据源!$D$4:$D$67)</f>
+        <f>折现数据源!U7*折现数据源!$D$7+折现数据源!V7*折现数据源!$D$7+折现数据源!W7*折现数据源!$D$7+折现数据源!X7*折现数据源!$D$7+折现数据源!Y7*折现数据源!$D$7+折现数据源!Z7*折现数据源!$D$7+折现数据源!AA7*折现数据源!$D$7</f>
         <v/>
       </c>
       <c r="G8" s="31">
@@ -8725,11 +8725,11 @@
         <v/>
       </c>
       <c r="E9" s="29">
-        <f>SUMPRODUCT(折现数据源!E$4:E$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!F$4:F$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!G$4:G$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!H$4:H$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!I$4:I$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!J$4:J$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!K$4:K$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!L$4:L$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!M$4:M$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!N$4:N$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!O$4:O$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!P$4:P$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Q$4:Q$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!R$4:R$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!S$4:S$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!T$4:T$67,折现数据源!$D$4:$D$67)</f>
+        <f>折现数据源!E8*折现数据源!$D$8+折现数据源!F8*折现数据源!$D$8+折现数据源!G8*折现数据源!$D$8+折现数据源!H8*折现数据源!$D$8+折现数据源!I8*折现数据源!$D$8+折现数据源!J8*折现数据源!$D$8+折现数据源!K8*折现数据源!$D$8+折现数据源!L8*折现数据源!$D$8+折现数据源!M8*折现数据源!$D$8+折现数据源!N8*折现数据源!$D$8+折现数据源!O8*折现数据源!$D$8+折现数据源!P8*折现数据源!$D$8+折现数据源!Q8*折现数据源!$D$8+折现数据源!R8*折现数据源!$D$8+折现数据源!S8*折现数据源!$D$8+折现数据源!T8*折现数据源!$D$8</f>
         <v/>
       </c>
       <c r="F9" s="29">
-        <f>SUMPRODUCT(折现数据源!U$4:U$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!V$4:V$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!W$4:W$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!X$4:X$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Y$4:Y$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Z$4:Z$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!AA$4:AA$67,折现数据源!$D$4:$D$67)</f>
+        <f>折现数据源!U8*折现数据源!$D$8+折现数据源!V8*折现数据源!$D$8+折现数据源!W8*折现数据源!$D$8+折现数据源!X8*折现数据源!$D$8+折现数据源!Y8*折现数据源!$D$8+折现数据源!Z8*折现数据源!$D$8+折现数据源!AA8*折现数据源!$D$8</f>
         <v/>
       </c>
       <c r="G9" s="31">
@@ -8759,11 +8759,11 @@
         <v/>
       </c>
       <c r="E10" s="29">
-        <f>SUMPRODUCT(折现数据源!E$4:E$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!F$4:F$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!G$4:G$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!H$4:H$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!I$4:I$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!J$4:J$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!K$4:K$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!L$4:L$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!M$4:M$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!N$4:N$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!O$4:O$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!P$4:P$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Q$4:Q$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!R$4:R$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!S$4:S$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!T$4:T$67,折现数据源!$D$4:$D$67)</f>
+        <f>折现数据源!E9*折现数据源!$D$9+折现数据源!F9*折现数据源!$D$9+折现数据源!G9*折现数据源!$D$9+折现数据源!H9*折现数据源!$D$9+折现数据源!I9*折现数据源!$D$9+折现数据源!J9*折现数据源!$D$9+折现数据源!K9*折现数据源!$D$9+折现数据源!L9*折现数据源!$D$9+折现数据源!M9*折现数据源!$D$9+折现数据源!N9*折现数据源!$D$9+折现数据源!O9*折现数据源!$D$9+折现数据源!P9*折现数据源!$D$9+折现数据源!Q9*折现数据源!$D$9+折现数据源!R9*折现数据源!$D$9+折现数据源!S9*折现数据源!$D$9+折现数据源!T9*折现数据源!$D$9</f>
         <v/>
       </c>
       <c r="F10" s="29">
-        <f>SUMPRODUCT(折现数据源!U$4:U$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!V$4:V$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!W$4:W$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!X$4:X$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Y$4:Y$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Z$4:Z$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!AA$4:AA$67,折现数据源!$D$4:$D$67)</f>
+        <f>折现数据源!U9*折现数据源!$D$9+折现数据源!V9*折现数据源!$D$9+折现数据源!W9*折现数据源!$D$9+折现数据源!X9*折现数据源!$D$9+折现数据源!Y9*折现数据源!$D$9+折现数据源!Z9*折现数据源!$D$9+折现数据源!AA9*折现数据源!$D$9</f>
         <v/>
       </c>
       <c r="G10" s="31">
@@ -8793,11 +8793,11 @@
         <v/>
       </c>
       <c r="E11" s="29">
-        <f>SUMPRODUCT(折现数据源!E$4:E$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!F$4:F$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!G$4:G$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!H$4:H$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!I$4:I$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!J$4:J$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!K$4:K$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!L$4:L$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!M$4:M$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!N$4:N$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!O$4:O$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!P$4:P$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Q$4:Q$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!R$4:R$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!S$4:S$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!T$4:T$67,折现数据源!$D$4:$D$67)</f>
+        <f>折现数据源!E10*折现数据源!$D$10+折现数据源!F10*折现数据源!$D$10+折现数据源!G10*折现数据源!$D$10+折现数据源!H10*折现数据源!$D$10+折现数据源!I10*折现数据源!$D$10+折现数据源!J10*折现数据源!$D$10+折现数据源!K10*折现数据源!$D$10+折现数据源!L10*折现数据源!$D$10+折现数据源!M10*折现数据源!$D$10+折现数据源!N10*折现数据源!$D$10+折现数据源!O10*折现数据源!$D$10+折现数据源!P10*折现数据源!$D$10+折现数据源!Q10*折现数据源!$D$10+折现数据源!R10*折现数据源!$D$10+折现数据源!S10*折现数据源!$D$10+折现数据源!T10*折现数据源!$D$10</f>
         <v/>
       </c>
       <c r="F11" s="29">
-        <f>SUMPRODUCT(折现数据源!U$4:U$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!V$4:V$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!W$4:W$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!X$4:X$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Y$4:Y$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Z$4:Z$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!AA$4:AA$67,折现数据源!$D$4:$D$67)</f>
+        <f>折现数据源!U10*折现数据源!$D$10+折现数据源!V10*折现数据源!$D$10+折现数据源!W10*折现数据源!$D$10+折现数据源!X10*折现数据源!$D$10+折现数据源!Y10*折现数据源!$D$10+折现数据源!Z10*折现数据源!$D$10+折现数据源!AA10*折现数据源!$D$10</f>
         <v/>
       </c>
       <c r="G11" s="31">
@@ -8827,11 +8827,11 @@
         <v/>
       </c>
       <c r="E12" s="29">
-        <f>SUMPRODUCT(折现数据源!E$4:E$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!F$4:F$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!G$4:G$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!H$4:H$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!I$4:I$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!J$4:J$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!K$4:K$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!L$4:L$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!M$4:M$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!N$4:N$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!O$4:O$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!P$4:P$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Q$4:Q$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!R$4:R$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!S$4:S$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!T$4:T$67,折现数据源!$D$4:$D$67)</f>
+        <f>折现数据源!E11*折现数据源!$D$11+折现数据源!F11*折现数据源!$D$11+折现数据源!G11*折现数据源!$D$11+折现数据源!H11*折现数据源!$D$11+折现数据源!I11*折现数据源!$D$11+折现数据源!J11*折现数据源!$D$11+折现数据源!K11*折现数据源!$D$11+折现数据源!L11*折现数据源!$D$11+折现数据源!M11*折现数据源!$D$11+折现数据源!N11*折现数据源!$D$11+折现数据源!O11*折现数据源!$D$11+折现数据源!P11*折现数据源!$D$11+折现数据源!Q11*折现数据源!$D$11+折现数据源!R11*折现数据源!$D$11+折现数据源!S11*折现数据源!$D$11+折现数据源!T11*折现数据源!$D$11</f>
         <v/>
       </c>
       <c r="F12" s="29">
-        <f>SUMPRODUCT(折现数据源!U$4:U$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!V$4:V$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!W$4:W$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!X$4:X$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Y$4:Y$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Z$4:Z$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!AA$4:AA$67,折现数据源!$D$4:$D$67)</f>
+        <f>折现数据源!U11*折现数据源!$D$11+折现数据源!V11*折现数据源!$D$11+折现数据源!W11*折现数据源!$D$11+折现数据源!X11*折现数据源!$D$11+折现数据源!Y11*折现数据源!$D$11+折现数据源!Z11*折现数据源!$D$11+折现数据源!AA11*折现数据源!$D$11</f>
         <v/>
       </c>
       <c r="G12" s="31">
@@ -8861,11 +8861,11 @@
         <v/>
       </c>
       <c r="E13" s="29">
-        <f>SUMPRODUCT(折现数据源!E$4:E$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!F$4:F$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!G$4:G$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!H$4:H$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!I$4:I$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!J$4:J$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!K$4:K$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!L$4:L$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!M$4:M$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!N$4:N$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!O$4:O$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!P$4:P$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Q$4:Q$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!R$4:R$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!S$4:S$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!T$4:T$67,折现数据源!$D$4:$D$67)</f>
+        <f>折现数据源!E12*折现数据源!$D$12+折现数据源!F12*折现数据源!$D$12+折现数据源!G12*折现数据源!$D$12+折现数据源!H12*折现数据源!$D$12+折现数据源!I12*折现数据源!$D$12+折现数据源!J12*折现数据源!$D$12+折现数据源!K12*折现数据源!$D$12+折现数据源!L12*折现数据源!$D$12+折现数据源!M12*折现数据源!$D$12+折现数据源!N12*折现数据源!$D$12+折现数据源!O12*折现数据源!$D$12+折现数据源!P12*折现数据源!$D$12+折现数据源!Q12*折现数据源!$D$12+折现数据源!R12*折现数据源!$D$12+折现数据源!S12*折现数据源!$D$12+折现数据源!T12*折现数据源!$D$12</f>
         <v/>
       </c>
       <c r="F13" s="29">
-        <f>SUMPRODUCT(折现数据源!U$4:U$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!V$4:V$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!W$4:W$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!X$4:X$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Y$4:Y$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Z$4:Z$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!AA$4:AA$67,折现数据源!$D$4:$D$67)</f>
+        <f>折现数据源!U12*折现数据源!$D$12+折现数据源!V12*折现数据源!$D$12+折现数据源!W12*折现数据源!$D$12+折现数据源!X12*折现数据源!$D$12+折现数据源!Y12*折现数据源!$D$12+折现数据源!Z12*折现数据源!$D$12+折现数据源!AA12*折现数据源!$D$12</f>
         <v/>
       </c>
       <c r="G13" s="31">
@@ -8895,11 +8895,11 @@
         <v/>
       </c>
       <c r="E14" s="29">
-        <f>SUMPRODUCT(折现数据源!E$4:E$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!F$4:F$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!G$4:G$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!H$4:H$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!I$4:I$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!J$4:J$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!K$4:K$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!L$4:L$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!M$4:M$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!N$4:N$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!O$4:O$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!P$4:P$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Q$4:Q$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!R$4:R$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!S$4:S$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!T$4:T$67,折现数据源!$D$4:$D$67)</f>
+        <f>折现数据源!E13*折现数据源!$D$13+折现数据源!F13*折现数据源!$D$13+折现数据源!G13*折现数据源!$D$13+折现数据源!H13*折现数据源!$D$13+折现数据源!I13*折现数据源!$D$13+折现数据源!J13*折现数据源!$D$13+折现数据源!K13*折现数据源!$D$13+折现数据源!L13*折现数据源!$D$13+折现数据源!M13*折现数据源!$D$13+折现数据源!N13*折现数据源!$D$13+折现数据源!O13*折现数据源!$D$13+折现数据源!P13*折现数据源!$D$13+折现数据源!Q13*折现数据源!$D$13+折现数据源!R13*折现数据源!$D$13+折现数据源!S13*折现数据源!$D$13+折现数据源!T13*折现数据源!$D$13</f>
         <v/>
       </c>
       <c r="F14" s="29">
-        <f>SUMPRODUCT(折现数据源!U$4:U$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!V$4:V$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!W$4:W$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!X$4:X$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Y$4:Y$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Z$4:Z$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!AA$4:AA$67,折现数据源!$D$4:$D$67)</f>
+        <f>折现数据源!U13*折现数据源!$D$13+折现数据源!V13*折现数据源!$D$13+折现数据源!W13*折现数据源!$D$13+折现数据源!X13*折现数据源!$D$13+折现数据源!Y13*折现数据源!$D$13+折现数据源!Z13*折现数据源!$D$13+折现数据源!AA13*折现数据源!$D$13</f>
         <v/>
       </c>
       <c r="G14" s="31">
@@ -8929,11 +8929,11 @@
         <v/>
       </c>
       <c r="E15" s="29">
-        <f>SUMPRODUCT(折现数据源!E$4:E$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!F$4:F$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!G$4:G$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!H$4:H$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!I$4:I$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!J$4:J$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!K$4:K$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!L$4:L$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!M$4:M$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!N$4:N$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!O$4:O$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!P$4:P$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Q$4:Q$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!R$4:R$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!S$4:S$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!T$4:T$67,折现数据源!$D$4:$D$67)</f>
+        <f>折现数据源!E14*折现数据源!$D$14+折现数据源!F14*折现数据源!$D$14+折现数据源!G14*折现数据源!$D$14+折现数据源!H14*折现数据源!$D$14+折现数据源!I14*折现数据源!$D$14+折现数据源!J14*折现数据源!$D$14+折现数据源!K14*折现数据源!$D$14+折现数据源!L14*折现数据源!$D$14+折现数据源!M14*折现数据源!$D$14+折现数据源!N14*折现数据源!$D$14+折现数据源!O14*折现数据源!$D$14+折现数据源!P14*折现数据源!$D$14+折现数据源!Q14*折现数据源!$D$14+折现数据源!R14*折现数据源!$D$14+折现数据源!S14*折现数据源!$D$14+折现数据源!T14*折现数据源!$D$14</f>
         <v/>
       </c>
       <c r="F15" s="29">
-        <f>SUMPRODUCT(折现数据源!U$4:U$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!V$4:V$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!W$4:W$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!X$4:X$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Y$4:Y$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Z$4:Z$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!AA$4:AA$67,折现数据源!$D$4:$D$67)</f>
+        <f>折现数据源!U14*折现数据源!$D$14+折现数据源!V14*折现数据源!$D$14+折现数据源!W14*折现数据源!$D$14+折现数据源!X14*折现数据源!$D$14+折现数据源!Y14*折现数据源!$D$14+折现数据源!Z14*折现数据源!$D$14+折现数据源!AA14*折现数据源!$D$14</f>
         <v/>
       </c>
       <c r="G15" s="31">
@@ -8963,11 +8963,11 @@
         <v/>
       </c>
       <c r="E16" s="29">
-        <f>SUMPRODUCT(折现数据源!E$4:E$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!F$4:F$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!G$4:G$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!H$4:H$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!I$4:I$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!J$4:J$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!K$4:K$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!L$4:L$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!M$4:M$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!N$4:N$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!O$4:O$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!P$4:P$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Q$4:Q$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!R$4:R$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!S$4:S$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!T$4:T$67,折现数据源!$D$4:$D$67)</f>
+        <f>折现数据源!E15*折现数据源!$D$15+折现数据源!F15*折现数据源!$D$15+折现数据源!G15*折现数据源!$D$15+折现数据源!H15*折现数据源!$D$15+折现数据源!I15*折现数据源!$D$15+折现数据源!J15*折现数据源!$D$15+折现数据源!K15*折现数据源!$D$15+折现数据源!L15*折现数据源!$D$15+折现数据源!M15*折现数据源!$D$15+折现数据源!N15*折现数据源!$D$15+折现数据源!O15*折现数据源!$D$15+折现数据源!P15*折现数据源!$D$15+折现数据源!Q15*折现数据源!$D$15+折现数据源!R15*折现数据源!$D$15+折现数据源!S15*折现数据源!$D$15+折现数据源!T15*折现数据源!$D$15</f>
         <v/>
       </c>
       <c r="F16" s="29">
-        <f>SUMPRODUCT(折现数据源!U$4:U$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!V$4:V$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!W$4:W$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!X$4:X$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Y$4:Y$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Z$4:Z$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!AA$4:AA$67,折现数据源!$D$4:$D$67)</f>
+        <f>折现数据源!U15*折现数据源!$D$15+折现数据源!V15*折现数据源!$D$15+折现数据源!W15*折现数据源!$D$15+折现数据源!X15*折现数据源!$D$15+折现数据源!Y15*折现数据源!$D$15+折现数据源!Z15*折现数据源!$D$15+折现数据源!AA15*折现数据源!$D$15</f>
         <v/>
       </c>
       <c r="G16" s="31">
@@ -8997,11 +8997,11 @@
         <v/>
       </c>
       <c r="E17" s="29">
-        <f>SUMPRODUCT(折现数据源!E$4:E$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!F$4:F$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!G$4:G$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!H$4:H$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!I$4:I$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!J$4:J$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!K$4:K$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!L$4:L$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!M$4:M$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!N$4:N$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!O$4:O$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!P$4:P$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Q$4:Q$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!R$4:R$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!S$4:S$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!T$4:T$67,折现数据源!$D$4:$D$67)</f>
+        <f>折现数据源!E16*折现数据源!$D$16+折现数据源!F16*折现数据源!$D$16+折现数据源!G16*折现数据源!$D$16+折现数据源!H16*折现数据源!$D$16+折现数据源!I16*折现数据源!$D$16+折现数据源!J16*折现数据源!$D$16+折现数据源!K16*折现数据源!$D$16+折现数据源!L16*折现数据源!$D$16+折现数据源!M16*折现数据源!$D$16+折现数据源!N16*折现数据源!$D$16+折现数据源!O16*折现数据源!$D$16+折现数据源!P16*折现数据源!$D$16+折现数据源!Q16*折现数据源!$D$16+折现数据源!R16*折现数据源!$D$16+折现数据源!S16*折现数据源!$D$16+折现数据源!T16*折现数据源!$D$16</f>
         <v/>
       </c>
       <c r="F17" s="29">
-        <f>SUMPRODUCT(折现数据源!U$4:U$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!V$4:V$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!W$4:W$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!X$4:X$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Y$4:Y$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Z$4:Z$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!AA$4:AA$67,折现数据源!$D$4:$D$67)</f>
+        <f>折现数据源!U16*折现数据源!$D$16+折现数据源!V16*折现数据源!$D$16+折现数据源!W16*折现数据源!$D$16+折现数据源!X16*折现数据源!$D$16+折现数据源!Y16*折现数据源!$D$16+折现数据源!Z16*折现数据源!$D$16+折现数据源!AA16*折现数据源!$D$16</f>
         <v/>
       </c>
       <c r="G17" s="31">
@@ -9031,11 +9031,11 @@
         <v/>
       </c>
       <c r="E18" s="29">
-        <f>SUMPRODUCT(折现数据源!E$4:E$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!F$4:F$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!G$4:G$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!H$4:H$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!I$4:I$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!J$4:J$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!K$4:K$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!L$4:L$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!M$4:M$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!N$4:N$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!O$4:O$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!P$4:P$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Q$4:Q$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!R$4:R$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!S$4:S$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!T$4:T$67,折现数据源!$D$4:$D$67)</f>
+        <f>折现数据源!E17*折现数据源!$D$17+折现数据源!F17*折现数据源!$D$17+折现数据源!G17*折现数据源!$D$17+折现数据源!H17*折现数据源!$D$17+折现数据源!I17*折现数据源!$D$17+折现数据源!J17*折现数据源!$D$17+折现数据源!K17*折现数据源!$D$17+折现数据源!L17*折现数据源!$D$17+折现数据源!M17*折现数据源!$D$17+折现数据源!N17*折现数据源!$D$17+折现数据源!O17*折现数据源!$D$17+折现数据源!P17*折现数据源!$D$17+折现数据源!Q17*折现数据源!$D$17+折现数据源!R17*折现数据源!$D$17+折现数据源!S17*折现数据源!$D$17+折现数据源!T17*折现数据源!$D$17</f>
         <v/>
       </c>
       <c r="F18" s="29">
-        <f>SUMPRODUCT(折现数据源!U$4:U$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!V$4:V$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!W$4:W$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!X$4:X$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Y$4:Y$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Z$4:Z$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!AA$4:AA$67,折现数据源!$D$4:$D$67)</f>
+        <f>折现数据源!U17*折现数据源!$D$17+折现数据源!V17*折现数据源!$D$17+折现数据源!W17*折现数据源!$D$17+折现数据源!X17*折现数据源!$D$17+折现数据源!Y17*折现数据源!$D$17+折现数据源!Z17*折现数据源!$D$17+折现数据源!AA17*折现数据源!$D$17</f>
         <v/>
       </c>
       <c r="G18" s="31">
@@ -9065,11 +9065,11 @@
         <v/>
       </c>
       <c r="E19" s="29">
-        <f>SUMPRODUCT(折现数据源!E$4:E$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!F$4:F$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!G$4:G$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!H$4:H$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!I$4:I$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!J$4:J$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!K$4:K$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!L$4:L$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!M$4:M$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!N$4:N$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!O$4:O$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!P$4:P$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Q$4:Q$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!R$4:R$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!S$4:S$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!T$4:T$67,折现数据源!$D$4:$D$67)</f>
+        <f>折现数据源!E18*折现数据源!$D$18+折现数据源!F18*折现数据源!$D$18+折现数据源!G18*折现数据源!$D$18+折现数据源!H18*折现数据源!$D$18+折现数据源!I18*折现数据源!$D$18+折现数据源!J18*折现数据源!$D$18+折现数据源!K18*折现数据源!$D$18+折现数据源!L18*折现数据源!$D$18+折现数据源!M18*折现数据源!$D$18+折现数据源!N18*折现数据源!$D$18+折现数据源!O18*折现数据源!$D$18+折现数据源!P18*折现数据源!$D$18+折现数据源!Q18*折现数据源!$D$18+折现数据源!R18*折现数据源!$D$18+折现数据源!S18*折现数据源!$D$18+折现数据源!T18*折现数据源!$D$18</f>
         <v/>
       </c>
       <c r="F19" s="29">
-        <f>SUMPRODUCT(折现数据源!U$4:U$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!V$4:V$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!W$4:W$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!X$4:X$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Y$4:Y$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Z$4:Z$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!AA$4:AA$67,折现数据源!$D$4:$D$67)</f>
+        <f>折现数据源!U18*折现数据源!$D$18+折现数据源!V18*折现数据源!$D$18+折现数据源!W18*折现数据源!$D$18+折现数据源!X18*折现数据源!$D$18+折现数据源!Y18*折现数据源!$D$18+折现数据源!Z18*折现数据源!$D$18+折现数据源!AA18*折现数据源!$D$18</f>
         <v/>
       </c>
       <c r="G19" s="31">
@@ -9099,11 +9099,11 @@
         <v/>
       </c>
       <c r="E20" s="29">
-        <f>SUMPRODUCT(折现数据源!E$4:E$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!F$4:F$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!G$4:G$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!H$4:H$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!I$4:I$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!J$4:J$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!K$4:K$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!L$4:L$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!M$4:M$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!N$4:N$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!O$4:O$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!P$4:P$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Q$4:Q$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!R$4:R$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!S$4:S$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!T$4:T$67,折现数据源!$D$4:$D$67)</f>
+        <f>折现数据源!E19*折现数据源!$D$19+折现数据源!F19*折现数据源!$D$19+折现数据源!G19*折现数据源!$D$19+折现数据源!H19*折现数据源!$D$19+折现数据源!I19*折现数据源!$D$19+折现数据源!J19*折现数据源!$D$19+折现数据源!K19*折现数据源!$D$19+折现数据源!L19*折现数据源!$D$19+折现数据源!M19*折现数据源!$D$19+折现数据源!N19*折现数据源!$D$19+折现数据源!O19*折现数据源!$D$19+折现数据源!P19*折现数据源!$D$19+折现数据源!Q19*折现数据源!$D$19+折现数据源!R19*折现数据源!$D$19+折现数据源!S19*折现数据源!$D$19+折现数据源!T19*折现数据源!$D$19</f>
         <v/>
       </c>
       <c r="F20" s="29">
-        <f>SUMPRODUCT(折现数据源!U$4:U$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!V$4:V$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!W$4:W$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!X$4:X$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Y$4:Y$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Z$4:Z$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!AA$4:AA$67,折现数据源!$D$4:$D$67)</f>
+        <f>折现数据源!U19*折现数据源!$D$19+折现数据源!V19*折现数据源!$D$19+折现数据源!W19*折现数据源!$D$19+折现数据源!X19*折现数据源!$D$19+折现数据源!Y19*折现数据源!$D$19+折现数据源!Z19*折现数据源!$D$19+折现数据源!AA19*折现数据源!$D$19</f>
         <v/>
       </c>
       <c r="G20" s="31">
@@ -9133,11 +9133,11 @@
         <v/>
       </c>
       <c r="E21" s="29">
-        <f>SUMPRODUCT(折现数据源!E$4:E$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!F$4:F$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!G$4:G$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!H$4:H$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!I$4:I$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!J$4:J$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!K$4:K$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!L$4:L$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!M$4:M$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!N$4:N$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!O$4:O$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!P$4:P$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Q$4:Q$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!R$4:R$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!S$4:S$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!T$4:T$67,折现数据源!$D$4:$D$67)</f>
+        <f>折现数据源!E20*折现数据源!$D$20+折现数据源!F20*折现数据源!$D$20+折现数据源!G20*折现数据源!$D$20+折现数据源!H20*折现数据源!$D$20+折现数据源!I20*折现数据源!$D$20+折现数据源!J20*折现数据源!$D$20+折现数据源!K20*折现数据源!$D$20+折现数据源!L20*折现数据源!$D$20+折现数据源!M20*折现数据源!$D$20+折现数据源!N20*折现数据源!$D$20+折现数据源!O20*折现数据源!$D$20+折现数据源!P20*折现数据源!$D$20+折现数据源!Q20*折现数据源!$D$20+折现数据源!R20*折现数据源!$D$20+折现数据源!S20*折现数据源!$D$20+折现数据源!T20*折现数据源!$D$20</f>
         <v/>
       </c>
       <c r="F21" s="29">
-        <f>SUMPRODUCT(折现数据源!U$4:U$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!V$4:V$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!W$4:W$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!X$4:X$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Y$4:Y$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Z$4:Z$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!AA$4:AA$67,折现数据源!$D$4:$D$67)</f>
+        <f>折现数据源!U20*折现数据源!$D$20+折现数据源!V20*折现数据源!$D$20+折现数据源!W20*折现数据源!$D$20+折现数据源!X20*折现数据源!$D$20+折现数据源!Y20*折现数据源!$D$20+折现数据源!Z20*折现数据源!$D$20+折现数据源!AA20*折现数据源!$D$20</f>
         <v/>
       </c>
       <c r="G21" s="31">
@@ -9167,11 +9167,11 @@
         <v/>
       </c>
       <c r="E22" s="29">
-        <f>SUMPRODUCT(折现数据源!E$4:E$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!F$4:F$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!G$4:G$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!H$4:H$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!I$4:I$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!J$4:J$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!K$4:K$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!L$4:L$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!M$4:M$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!N$4:N$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!O$4:O$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!P$4:P$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Q$4:Q$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!R$4:R$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!S$4:S$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!T$4:T$67,折现数据源!$D$4:$D$67)</f>
+        <f>折现数据源!E21*折现数据源!$D$21+折现数据源!F21*折现数据源!$D$21+折现数据源!G21*折现数据源!$D$21+折现数据源!H21*折现数据源!$D$21+折现数据源!I21*折现数据源!$D$21+折现数据源!J21*折现数据源!$D$21+折现数据源!K21*折现数据源!$D$21+折现数据源!L21*折现数据源!$D$21+折现数据源!M21*折现数据源!$D$21+折现数据源!N21*折现数据源!$D$21+折现数据源!O21*折现数据源!$D$21+折现数据源!P21*折现数据源!$D$21+折现数据源!Q21*折现数据源!$D$21+折现数据源!R21*折现数据源!$D$21+折现数据源!S21*折现数据源!$D$21+折现数据源!T21*折现数据源!$D$21</f>
         <v/>
       </c>
       <c r="F22" s="29">
-        <f>SUMPRODUCT(折现数据源!U$4:U$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!V$4:V$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!W$4:W$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!X$4:X$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Y$4:Y$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Z$4:Z$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!AA$4:AA$67,折现数据源!$D$4:$D$67)</f>
+        <f>折现数据源!U21*折现数据源!$D$21+折现数据源!V21*折现数据源!$D$21+折现数据源!W21*折现数据源!$D$21+折现数据源!X21*折现数据源!$D$21+折现数据源!Y21*折现数据源!$D$21+折现数据源!Z21*折现数据源!$D$21+折现数据源!AA21*折现数据源!$D$21</f>
         <v/>
       </c>
       <c r="G22" s="31">
@@ -9201,11 +9201,11 @@
         <v/>
       </c>
       <c r="E23" s="29">
-        <f>SUMPRODUCT(折现数据源!E$4:E$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!F$4:F$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!G$4:G$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!H$4:H$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!I$4:I$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!J$4:J$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!K$4:K$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!L$4:L$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!M$4:M$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!N$4:N$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!O$4:O$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!P$4:P$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Q$4:Q$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!R$4:R$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!S$4:S$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!T$4:T$67,折现数据源!$D$4:$D$67)</f>
+        <f>折现数据源!E22*折现数据源!$D$22+折现数据源!F22*折现数据源!$D$22+折现数据源!G22*折现数据源!$D$22+折现数据源!H22*折现数据源!$D$22+折现数据源!I22*折现数据源!$D$22+折现数据源!J22*折现数据源!$D$22+折现数据源!K22*折现数据源!$D$22+折现数据源!L22*折现数据源!$D$22+折现数据源!M22*折现数据源!$D$22+折现数据源!N22*折现数据源!$D$22+折现数据源!O22*折现数据源!$D$22+折现数据源!P22*折现数据源!$D$22+折现数据源!Q22*折现数据源!$D$22+折现数据源!R22*折现数据源!$D$22+折现数据源!S22*折现数据源!$D$22+折现数据源!T22*折现数据源!$D$22</f>
         <v/>
       </c>
       <c r="F23" s="29">
-        <f>SUMPRODUCT(折现数据源!U$4:U$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!V$4:V$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!W$4:W$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!X$4:X$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Y$4:Y$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Z$4:Z$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!AA$4:AA$67,折现数据源!$D$4:$D$67)</f>
+        <f>折现数据源!U22*折现数据源!$D$22+折现数据源!V22*折现数据源!$D$22+折现数据源!W22*折现数据源!$D$22+折现数据源!X22*折现数据源!$D$22+折现数据源!Y22*折现数据源!$D$22+折现数据源!Z22*折现数据源!$D$22+折现数据源!AA22*折现数据源!$D$22</f>
         <v/>
       </c>
       <c r="G23" s="31">
@@ -9235,11 +9235,11 @@
         <v/>
       </c>
       <c r="E24" s="29">
-        <f>SUMPRODUCT(折现数据源!E$4:E$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!F$4:F$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!G$4:G$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!H$4:H$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!I$4:I$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!J$4:J$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!K$4:K$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!L$4:L$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!M$4:M$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!N$4:N$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!O$4:O$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!P$4:P$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Q$4:Q$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!R$4:R$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!S$4:S$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!T$4:T$67,折现数据源!$D$4:$D$67)</f>
+        <f>折现数据源!E23*折现数据源!$D$23+折现数据源!F23*折现数据源!$D$23+折现数据源!G23*折现数据源!$D$23+折现数据源!H23*折现数据源!$D$23+折现数据源!I23*折现数据源!$D$23+折现数据源!J23*折现数据源!$D$23+折现数据源!K23*折现数据源!$D$23+折现数据源!L23*折现数据源!$D$23+折现数据源!M23*折现数据源!$D$23+折现数据源!N23*折现数据源!$D$23+折现数据源!O23*折现数据源!$D$23+折现数据源!P23*折现数据源!$D$23+折现数据源!Q23*折现数据源!$D$23+折现数据源!R23*折现数据源!$D$23+折现数据源!S23*折现数据源!$D$23+折现数据源!T23*折现数据源!$D$23</f>
         <v/>
       </c>
       <c r="F24" s="29">
-        <f>SUMPRODUCT(折现数据源!U$4:U$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!V$4:V$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!W$4:W$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!X$4:X$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Y$4:Y$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Z$4:Z$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!AA$4:AA$67,折现数据源!$D$4:$D$67)</f>
+        <f>折现数据源!U23*折现数据源!$D$23+折现数据源!V23*折现数据源!$D$23+折现数据源!W23*折现数据源!$D$23+折现数据源!X23*折现数据源!$D$23+折现数据源!Y23*折现数据源!$D$23+折现数据源!Z23*折现数据源!$D$23+折现数据源!AA23*折现数据源!$D$23</f>
         <v/>
       </c>
       <c r="G24" s="31">
@@ -9269,11 +9269,11 @@
         <v/>
       </c>
       <c r="E25" s="29">
-        <f>SUMPRODUCT(折现数据源!E$4:E$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!F$4:F$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!G$4:G$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!H$4:H$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!I$4:I$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!J$4:J$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!K$4:K$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!L$4:L$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!M$4:M$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!N$4:N$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!O$4:O$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!P$4:P$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Q$4:Q$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!R$4:R$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!S$4:S$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!T$4:T$67,折现数据源!$D$4:$D$67)</f>
+        <f>折现数据源!E24*折现数据源!$D$24+折现数据源!F24*折现数据源!$D$24+折现数据源!G24*折现数据源!$D$24+折现数据源!H24*折现数据源!$D$24+折现数据源!I24*折现数据源!$D$24+折现数据源!J24*折现数据源!$D$24+折现数据源!K24*折现数据源!$D$24+折现数据源!L24*折现数据源!$D$24+折现数据源!M24*折现数据源!$D$24+折现数据源!N24*折现数据源!$D$24+折现数据源!O24*折现数据源!$D$24+折现数据源!P24*折现数据源!$D$24+折现数据源!Q24*折现数据源!$D$24+折现数据源!R24*折现数据源!$D$24+折现数据源!S24*折现数据源!$D$24+折现数据源!T24*折现数据源!$D$24</f>
         <v/>
       </c>
       <c r="F25" s="29">
-        <f>SUMPRODUCT(折现数据源!U$4:U$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!V$4:V$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!W$4:W$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!X$4:X$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Y$4:Y$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Z$4:Z$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!AA$4:AA$67,折现数据源!$D$4:$D$67)</f>
+        <f>折现数据源!U24*折现数据源!$D$24+折现数据源!V24*折现数据源!$D$24+折现数据源!W24*折现数据源!$D$24+折现数据源!X24*折现数据源!$D$24+折现数据源!Y24*折现数据源!$D$24+折现数据源!Z24*折现数据源!$D$24+折现数据源!AA24*折现数据源!$D$24</f>
         <v/>
       </c>
       <c r="G25" s="31">
@@ -9303,11 +9303,11 @@
         <v/>
       </c>
       <c r="E26" s="29">
-        <f>SUMPRODUCT(折现数据源!E$4:E$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!F$4:F$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!G$4:G$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!H$4:H$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!I$4:I$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!J$4:J$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!K$4:K$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!L$4:L$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!M$4:M$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!N$4:N$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!O$4:O$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!P$4:P$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Q$4:Q$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!R$4:R$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!S$4:S$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!T$4:T$67,折现数据源!$D$4:$D$67)</f>
+        <f>折现数据源!E25*折现数据源!$D$25+折现数据源!F25*折现数据源!$D$25+折现数据源!G25*折现数据源!$D$25+折现数据源!H25*折现数据源!$D$25+折现数据源!I25*折现数据源!$D$25+折现数据源!J25*折现数据源!$D$25+折现数据源!K25*折现数据源!$D$25+折现数据源!L25*折现数据源!$D$25+折现数据源!M25*折现数据源!$D$25+折现数据源!N25*折现数据源!$D$25+折现数据源!O25*折现数据源!$D$25+折现数据源!P25*折现数据源!$D$25+折现数据源!Q25*折现数据源!$D$25+折现数据源!R25*折现数据源!$D$25+折现数据源!S25*折现数据源!$D$25+折现数据源!T25*折现数据源!$D$25</f>
         <v/>
       </c>
       <c r="F26" s="29">
-        <f>SUMPRODUCT(折现数据源!U$4:U$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!V$4:V$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!W$4:W$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!X$4:X$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Y$4:Y$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Z$4:Z$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!AA$4:AA$67,折现数据源!$D$4:$D$67)</f>
+        <f>折现数据源!U25*折现数据源!$D$25+折现数据源!V25*折现数据源!$D$25+折现数据源!W25*折现数据源!$D$25+折现数据源!X25*折现数据源!$D$25+折现数据源!Y25*折现数据源!$D$25+折现数据源!Z25*折现数据源!$D$25+折现数据源!AA25*折现数据源!$D$25</f>
         <v/>
       </c>
       <c r="G26" s="31">
@@ -9337,11 +9337,11 @@
         <v/>
       </c>
       <c r="E27" s="29">
-        <f>SUMPRODUCT(折现数据源!E$4:E$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!F$4:F$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!G$4:G$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!H$4:H$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!I$4:I$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!J$4:J$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!K$4:K$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!L$4:L$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!M$4:M$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!N$4:N$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!O$4:O$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!P$4:P$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Q$4:Q$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!R$4:R$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!S$4:S$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!T$4:T$67,折现数据源!$D$4:$D$67)</f>
+        <f>折现数据源!E26*折现数据源!$D$26+折现数据源!F26*折现数据源!$D$26+折现数据源!G26*折现数据源!$D$26+折现数据源!H26*折现数据源!$D$26+折现数据源!I26*折现数据源!$D$26+折现数据源!J26*折现数据源!$D$26+折现数据源!K26*折现数据源!$D$26+折现数据源!L26*折现数据源!$D$26+折现数据源!M26*折现数据源!$D$26+折现数据源!N26*折现数据源!$D$26+折现数据源!O26*折现数据源!$D$26+折现数据源!P26*折现数据源!$D$26+折现数据源!Q26*折现数据源!$D$26+折现数据源!R26*折现数据源!$D$26+折现数据源!S26*折现数据源!$D$26+折现数据源!T26*折现数据源!$D$26</f>
         <v/>
       </c>
       <c r="F27" s="29">
-        <f>SUMPRODUCT(折现数据源!U$4:U$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!V$4:V$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!W$4:W$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!X$4:X$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Y$4:Y$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Z$4:Z$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!AA$4:AA$67,折现数据源!$D$4:$D$67)</f>
+        <f>折现数据源!U26*折现数据源!$D$26+折现数据源!V26*折现数据源!$D$26+折现数据源!W26*折现数据源!$D$26+折现数据源!X26*折现数据源!$D$26+折现数据源!Y26*折现数据源!$D$26+折现数据源!Z26*折现数据源!$D$26+折现数据源!AA26*折现数据源!$D$26</f>
         <v/>
       </c>
       <c r="G27" s="31">
@@ -9371,11 +9371,11 @@
         <v/>
       </c>
       <c r="E28" s="29">
-        <f>SUMPRODUCT(折现数据源!E$4:E$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!F$4:F$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!G$4:G$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!H$4:H$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!I$4:I$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!J$4:J$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!K$4:K$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!L$4:L$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!M$4:M$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!N$4:N$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!O$4:O$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!P$4:P$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Q$4:Q$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!R$4:R$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!S$4:S$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!T$4:T$67,折现数据源!$D$4:$D$67)</f>
+        <f>折现数据源!E27*折现数据源!$D$27+折现数据源!F27*折现数据源!$D$27+折现数据源!G27*折现数据源!$D$27+折现数据源!H27*折现数据源!$D$27+折现数据源!I27*折现数据源!$D$27+折现数据源!J27*折现数据源!$D$27+折现数据源!K27*折现数据源!$D$27+折现数据源!L27*折现数据源!$D$27+折现数据源!M27*折现数据源!$D$27+折现数据源!N27*折现数据源!$D$27+折现数据源!O27*折现数据源!$D$27+折现数据源!P27*折现数据源!$D$27+折现数据源!Q27*折现数据源!$D$27+折现数据源!R27*折现数据源!$D$27+折现数据源!S27*折现数据源!$D$27+折现数据源!T27*折现数据源!$D$27</f>
         <v/>
       </c>
       <c r="F28" s="29">
-        <f>SUMPRODUCT(折现数据源!U$4:U$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!V$4:V$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!W$4:W$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!X$4:X$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Y$4:Y$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Z$4:Z$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!AA$4:AA$67,折现数据源!$D$4:$D$67)</f>
+        <f>折现数据源!U27*折现数据源!$D$27+折现数据源!V27*折现数据源!$D$27+折现数据源!W27*折现数据源!$D$27+折现数据源!X27*折现数据源!$D$27+折现数据源!Y27*折现数据源!$D$27+折现数据源!Z27*折现数据源!$D$27+折现数据源!AA27*折现数据源!$D$27</f>
         <v/>
       </c>
       <c r="G28" s="31">
@@ -9405,11 +9405,11 @@
         <v/>
       </c>
       <c r="E29" s="29">
-        <f>SUMPRODUCT(折现数据源!E$4:E$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!F$4:F$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!G$4:G$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!H$4:H$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!I$4:I$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!J$4:J$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!K$4:K$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!L$4:L$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!M$4:M$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!N$4:N$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!O$4:O$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!P$4:P$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Q$4:Q$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!R$4:R$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!S$4:S$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!T$4:T$67,折现数据源!$D$4:$D$67)</f>
+        <f>折现数据源!E28*折现数据源!$D$28+折现数据源!F28*折现数据源!$D$28+折现数据源!G28*折现数据源!$D$28+折现数据源!H28*折现数据源!$D$28+折现数据源!I28*折现数据源!$D$28+折现数据源!J28*折现数据源!$D$28+折现数据源!K28*折现数据源!$D$28+折现数据源!L28*折现数据源!$D$28+折现数据源!M28*折现数据源!$D$28+折现数据源!N28*折现数据源!$D$28+折现数据源!O28*折现数据源!$D$28+折现数据源!P28*折现数据源!$D$28+折现数据源!Q28*折现数据源!$D$28+折现数据源!R28*折现数据源!$D$28+折现数据源!S28*折现数据源!$D$28+折现数据源!T28*折现数据源!$D$28</f>
         <v/>
       </c>
       <c r="F29" s="29">
-        <f>SUMPRODUCT(折现数据源!U$4:U$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!V$4:V$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!W$4:W$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!X$4:X$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Y$4:Y$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Z$4:Z$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!AA$4:AA$67,折现数据源!$D$4:$D$67)</f>
+        <f>折现数据源!U28*折现数据源!$D$28+折现数据源!V28*折现数据源!$D$28+折现数据源!W28*折现数据源!$D$28+折现数据源!X28*折现数据源!$D$28+折现数据源!Y28*折现数据源!$D$28+折现数据源!Z28*折现数据源!$D$28+折现数据源!AA28*折现数据源!$D$28</f>
         <v/>
       </c>
       <c r="G29" s="31">
@@ -9439,11 +9439,11 @@
         <v/>
       </c>
       <c r="E30" s="29">
-        <f>SUMPRODUCT(折现数据源!E$4:E$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!F$4:F$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!G$4:G$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!H$4:H$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!I$4:I$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!J$4:J$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!K$4:K$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!L$4:L$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!M$4:M$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!N$4:N$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!O$4:O$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!P$4:P$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Q$4:Q$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!R$4:R$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!S$4:S$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!T$4:T$67,折现数据源!$D$4:$D$67)</f>
+        <f>折现数据源!E29*折现数据源!$D$29+折现数据源!F29*折现数据源!$D$29+折现数据源!G29*折现数据源!$D$29+折现数据源!H29*折现数据源!$D$29+折现数据源!I29*折现数据源!$D$29+折现数据源!J29*折现数据源!$D$29+折现数据源!K29*折现数据源!$D$29+折现数据源!L29*折现数据源!$D$29+折现数据源!M29*折现数据源!$D$29+折现数据源!N29*折现数据源!$D$29+折现数据源!O29*折现数据源!$D$29+折现数据源!P29*折现数据源!$D$29+折现数据源!Q29*折现数据源!$D$29+折现数据源!R29*折现数据源!$D$29+折现数据源!S29*折现数据源!$D$29+折现数据源!T29*折现数据源!$D$29</f>
         <v/>
       </c>
       <c r="F30" s="29">
-        <f>SUMPRODUCT(折现数据源!U$4:U$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!V$4:V$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!W$4:W$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!X$4:X$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Y$4:Y$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Z$4:Z$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!AA$4:AA$67,折现数据源!$D$4:$D$67)</f>
+        <f>折现数据源!U29*折现数据源!$D$29+折现数据源!V29*折现数据源!$D$29+折现数据源!W29*折现数据源!$D$29+折现数据源!X29*折现数据源!$D$29+折现数据源!Y29*折现数据源!$D$29+折现数据源!Z29*折现数据源!$D$29+折现数据源!AA29*折现数据源!$D$29</f>
         <v/>
       </c>
       <c r="G30" s="31">
@@ -9473,11 +9473,11 @@
         <v/>
       </c>
       <c r="E31" s="29">
-        <f>SUMPRODUCT(折现数据源!E$4:E$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!F$4:F$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!G$4:G$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!H$4:H$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!I$4:I$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!J$4:J$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!K$4:K$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!L$4:L$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!M$4:M$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!N$4:N$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!O$4:O$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!P$4:P$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Q$4:Q$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!R$4:R$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!S$4:S$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!T$4:T$67,折现数据源!$D$4:$D$67)</f>
+        <f>折现数据源!E30*折现数据源!$D$30+折现数据源!F30*折现数据源!$D$30+折现数据源!G30*折现数据源!$D$30+折现数据源!H30*折现数据源!$D$30+折现数据源!I30*折现数据源!$D$30+折现数据源!J30*折现数据源!$D$30+折现数据源!K30*折现数据源!$D$30+折现数据源!L30*折现数据源!$D$30+折现数据源!M30*折现数据源!$D$30+折现数据源!N30*折现数据源!$D$30+折现数据源!O30*折现数据源!$D$30+折现数据源!P30*折现数据源!$D$30+折现数据源!Q30*折现数据源!$D$30+折现数据源!R30*折现数据源!$D$30+折现数据源!S30*折现数据源!$D$30+折现数据源!T30*折现数据源!$D$30</f>
         <v/>
       </c>
       <c r="F31" s="29">
-        <f>SUMPRODUCT(折现数据源!U$4:U$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!V$4:V$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!W$4:W$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!X$4:X$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Y$4:Y$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Z$4:Z$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!AA$4:AA$67,折现数据源!$D$4:$D$67)</f>
+        <f>折现数据源!U30*折现数据源!$D$30+折现数据源!V30*折现数据源!$D$30+折现数据源!W30*折现数据源!$D$30+折现数据源!X30*折现数据源!$D$30+折现数据源!Y30*折现数据源!$D$30+折现数据源!Z30*折现数据源!$D$30+折现数据源!AA30*折现数据源!$D$30</f>
         <v/>
       </c>
       <c r="G31" s="31">
@@ -9507,11 +9507,11 @@
         <v/>
       </c>
       <c r="E32" s="29">
-        <f>SUMPRODUCT(折现数据源!E$4:E$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!F$4:F$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!G$4:G$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!H$4:H$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!I$4:I$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!J$4:J$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!K$4:K$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!L$4:L$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!M$4:M$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!N$4:N$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!O$4:O$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!P$4:P$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Q$4:Q$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!R$4:R$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!S$4:S$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!T$4:T$67,折现数据源!$D$4:$D$67)</f>
+        <f>折现数据源!E31*折现数据源!$D$31+折现数据源!F31*折现数据源!$D$31+折现数据源!G31*折现数据源!$D$31+折现数据源!H31*折现数据源!$D$31+折现数据源!I31*折现数据源!$D$31+折现数据源!J31*折现数据源!$D$31+折现数据源!K31*折现数据源!$D$31+折现数据源!L31*折现数据源!$D$31+折现数据源!M31*折现数据源!$D$31+折现数据源!N31*折现数据源!$D$31+折现数据源!O31*折现数据源!$D$31+折现数据源!P31*折现数据源!$D$31+折现数据源!Q31*折现数据源!$D$31+折现数据源!R31*折现数据源!$D$31+折现数据源!S31*折现数据源!$D$31+折现数据源!T31*折现数据源!$D$31</f>
         <v/>
       </c>
       <c r="F32" s="29">
-        <f>SUMPRODUCT(折现数据源!U$4:U$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!V$4:V$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!W$4:W$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!X$4:X$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Y$4:Y$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Z$4:Z$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!AA$4:AA$67,折现数据源!$D$4:$D$67)</f>
+        <f>折现数据源!U31*折现数据源!$D$31+折现数据源!V31*折现数据源!$D$31+折现数据源!W31*折现数据源!$D$31+折现数据源!X31*折现数据源!$D$31+折现数据源!Y31*折现数据源!$D$31+折现数据源!Z31*折现数据源!$D$31+折现数据源!AA31*折现数据源!$D$31</f>
         <v/>
       </c>
       <c r="G32" s="31">
@@ -9541,11 +9541,11 @@
         <v/>
       </c>
       <c r="E33" s="29">
-        <f>SUMPRODUCT(折现数据源!E$4:E$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!F$4:F$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!G$4:G$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!H$4:H$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!I$4:I$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!J$4:J$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!K$4:K$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!L$4:L$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!M$4:M$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!N$4:N$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!O$4:O$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!P$4:P$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Q$4:Q$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!R$4:R$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!S$4:S$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!T$4:T$67,折现数据源!$D$4:$D$67)</f>
+        <f>折现数据源!E32*折现数据源!$D$32+折现数据源!F32*折现数据源!$D$32+折现数据源!G32*折现数据源!$D$32+折现数据源!H32*折现数据源!$D$32+折现数据源!I32*折现数据源!$D$32+折现数据源!J32*折现数据源!$D$32+折现数据源!K32*折现数据源!$D$32+折现数据源!L32*折现数据源!$D$32+折现数据源!M32*折现数据源!$D$32+折现数据源!N32*折现数据源!$D$32+折现数据源!O32*折现数据源!$D$32+折现数据源!P32*折现数据源!$D$32+折现数据源!Q32*折现数据源!$D$32+折现数据源!R32*折现数据源!$D$32+折现数据源!S32*折现数据源!$D$32+折现数据源!T32*折现数据源!$D$32</f>
         <v/>
       </c>
       <c r="F33" s="29">
-        <f>SUMPRODUCT(折现数据源!U$4:U$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!V$4:V$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!W$4:W$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!X$4:X$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Y$4:Y$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Z$4:Z$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!AA$4:AA$67,折现数据源!$D$4:$D$67)</f>
+        <f>折现数据源!U32*折现数据源!$D$32+折现数据源!V32*折现数据源!$D$32+折现数据源!W32*折现数据源!$D$32+折现数据源!X32*折现数据源!$D$32+折现数据源!Y32*折现数据源!$D$32+折现数据源!Z32*折现数据源!$D$32+折现数据源!AA32*折现数据源!$D$32</f>
         <v/>
       </c>
       <c r="G33" s="31">
@@ -9575,11 +9575,11 @@
         <v/>
       </c>
       <c r="E34" s="29">
-        <f>SUMPRODUCT(折现数据源!E$4:E$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!F$4:F$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!G$4:G$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!H$4:H$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!I$4:I$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!J$4:J$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!K$4:K$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!L$4:L$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!M$4:M$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!N$4:N$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!O$4:O$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!P$4:P$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Q$4:Q$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!R$4:R$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!S$4:S$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!T$4:T$67,折现数据源!$D$4:$D$67)</f>
+        <f>折现数据源!E33*折现数据源!$D$33+折现数据源!F33*折现数据源!$D$33+折现数据源!G33*折现数据源!$D$33+折现数据源!H33*折现数据源!$D$33+折现数据源!I33*折现数据源!$D$33+折现数据源!J33*折现数据源!$D$33+折现数据源!K33*折现数据源!$D$33+折现数据源!L33*折现数据源!$D$33+折现数据源!M33*折现数据源!$D$33+折现数据源!N33*折现数据源!$D$33+折现数据源!O33*折现数据源!$D$33+折现数据源!P33*折现数据源!$D$33+折现数据源!Q33*折现数据源!$D$33+折现数据源!R33*折现数据源!$D$33+折现数据源!S33*折现数据源!$D$33+折现数据源!T33*折现数据源!$D$33</f>
         <v/>
       </c>
       <c r="F34" s="29">
-        <f>SUMPRODUCT(折现数据源!U$4:U$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!V$4:V$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!W$4:W$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!X$4:X$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Y$4:Y$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Z$4:Z$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!AA$4:AA$67,折现数据源!$D$4:$D$67)</f>
+        <f>折现数据源!U33*折现数据源!$D$33+折现数据源!V33*折现数据源!$D$33+折现数据源!W33*折现数据源!$D$33+折现数据源!X33*折现数据源!$D$33+折现数据源!Y33*折现数据源!$D$33+折现数据源!Z33*折现数据源!$D$33+折现数据源!AA33*折现数据源!$D$33</f>
         <v/>
       </c>
       <c r="G34" s="31">
@@ -9609,11 +9609,11 @@
         <v/>
       </c>
       <c r="E35" s="29">
-        <f>SUMPRODUCT(折现数据源!E$4:E$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!F$4:F$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!G$4:G$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!H$4:H$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!I$4:I$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!J$4:J$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!K$4:K$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!L$4:L$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!M$4:M$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!N$4:N$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!O$4:O$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!P$4:P$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Q$4:Q$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!R$4:R$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!S$4:S$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!T$4:T$67,折现数据源!$D$4:$D$67)</f>
+        <f>折现数据源!E34*折现数据源!$D$34+折现数据源!F34*折现数据源!$D$34+折现数据源!G34*折现数据源!$D$34+折现数据源!H34*折现数据源!$D$34+折现数据源!I34*折现数据源!$D$34+折现数据源!J34*折现数据源!$D$34+折现数据源!K34*折现数据源!$D$34+折现数据源!L34*折现数据源!$D$34+折现数据源!M34*折现数据源!$D$34+折现数据源!N34*折现数据源!$D$34+折现数据源!O34*折现数据源!$D$34+折现数据源!P34*折现数据源!$D$34+折现数据源!Q34*折现数据源!$D$34+折现数据源!R34*折现数据源!$D$34+折现数据源!S34*折现数据源!$D$34+折现数据源!T34*折现数据源!$D$34</f>
         <v/>
       </c>
       <c r="F35" s="29">
-        <f>SUMPRODUCT(折现数据源!U$4:U$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!V$4:V$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!W$4:W$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!X$4:X$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Y$4:Y$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Z$4:Z$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!AA$4:AA$67,折现数据源!$D$4:$D$67)</f>
+        <f>折现数据源!U34*折现数据源!$D$34+折现数据源!V34*折现数据源!$D$34+折现数据源!W34*折现数据源!$D$34+折现数据源!X34*折现数据源!$D$34+折现数据源!Y34*折现数据源!$D$34+折现数据源!Z34*折现数据源!$D$34+折现数据源!AA34*折现数据源!$D$34</f>
         <v/>
       </c>
       <c r="G35" s="31">
@@ -9643,11 +9643,11 @@
         <v/>
       </c>
       <c r="E36" s="29">
-        <f>SUMPRODUCT(折现数据源!E$4:E$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!F$4:F$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!G$4:G$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!H$4:H$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!I$4:I$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!J$4:J$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!K$4:K$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!L$4:L$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!M$4:M$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!N$4:N$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!O$4:O$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!P$4:P$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Q$4:Q$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!R$4:R$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!S$4:S$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!T$4:T$67,折现数据源!$D$4:$D$67)</f>
+        <f>折现数据源!E35*折现数据源!$D$35+折现数据源!F35*折现数据源!$D$35+折现数据源!G35*折现数据源!$D$35+折现数据源!H35*折现数据源!$D$35+折现数据源!I35*折现数据源!$D$35+折现数据源!J35*折现数据源!$D$35+折现数据源!K35*折现数据源!$D$35+折现数据源!L35*折现数据源!$D$35+折现数据源!M35*折现数据源!$D$35+折现数据源!N35*折现数据源!$D$35+折现数据源!O35*折现数据源!$D$35+折现数据源!P35*折现数据源!$D$35+折现数据源!Q35*折现数据源!$D$35+折现数据源!R35*折现数据源!$D$35+折现数据源!S35*折现数据源!$D$35+折现数据源!T35*折现数据源!$D$35</f>
         <v/>
       </c>
       <c r="F36" s="29">
-        <f>SUMPRODUCT(折现数据源!U$4:U$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!V$4:V$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!W$4:W$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!X$4:X$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Y$4:Y$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Z$4:Z$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!AA$4:AA$67,折现数据源!$D$4:$D$67)</f>
+        <f>折现数据源!U35*折现数据源!$D$35+折现数据源!V35*折现数据源!$D$35+折现数据源!W35*折现数据源!$D$35+折现数据源!X35*折现数据源!$D$35+折现数据源!Y35*折现数据源!$D$35+折现数据源!Z35*折现数据源!$D$35+折现数据源!AA35*折现数据源!$D$35</f>
         <v/>
       </c>
       <c r="G36" s="31">
@@ -9677,11 +9677,11 @@
         <v/>
       </c>
       <c r="E37" s="29">
-        <f>SUMPRODUCT(折现数据源!E$4:E$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!F$4:F$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!G$4:G$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!H$4:H$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!I$4:I$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!J$4:J$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!K$4:K$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!L$4:L$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!M$4:M$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!N$4:N$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!O$4:O$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!P$4:P$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Q$4:Q$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!R$4:R$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!S$4:S$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!T$4:T$67,折现数据源!$D$4:$D$67)</f>
+        <f>折现数据源!E36*折现数据源!$D$36+折现数据源!F36*折现数据源!$D$36+折现数据源!G36*折现数据源!$D$36+折现数据源!H36*折现数据源!$D$36+折现数据源!I36*折现数据源!$D$36+折现数据源!J36*折现数据源!$D$36+折现数据源!K36*折现数据源!$D$36+折现数据源!L36*折现数据源!$D$36+折现数据源!M36*折现数据源!$D$36+折现数据源!N36*折现数据源!$D$36+折现数据源!O36*折现数据源!$D$36+折现数据源!P36*折现数据源!$D$36+折现数据源!Q36*折现数据源!$D$36+折现数据源!R36*折现数据源!$D$36+折现数据源!S36*折现数据源!$D$36+折现数据源!T36*折现数据源!$D$36</f>
         <v/>
       </c>
       <c r="F37" s="29">
-        <f>SUMPRODUCT(折现数据源!U$4:U$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!V$4:V$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!W$4:W$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!X$4:X$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Y$4:Y$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Z$4:Z$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!AA$4:AA$67,折现数据源!$D$4:$D$67)</f>
+        <f>折现数据源!U36*折现数据源!$D$36+折现数据源!V36*折现数据源!$D$36+折现数据源!W36*折现数据源!$D$36+折现数据源!X36*折现数据源!$D$36+折现数据源!Y36*折现数据源!$D$36+折现数据源!Z36*折现数据源!$D$36+折现数据源!AA36*折现数据源!$D$36</f>
         <v/>
       </c>
       <c r="G37" s="31">
@@ -9711,11 +9711,11 @@
         <v/>
       </c>
       <c r="E38" s="29">
-        <f>SUMPRODUCT(折现数据源!E$4:E$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!F$4:F$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!G$4:G$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!H$4:H$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!I$4:I$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!J$4:J$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!K$4:K$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!L$4:L$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!M$4:M$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!N$4:N$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!O$4:O$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!P$4:P$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Q$4:Q$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!R$4:R$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!S$4:S$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!T$4:T$67,折现数据源!$D$4:$D$67)</f>
+        <f>折现数据源!E37*折现数据源!$D$37+折现数据源!F37*折现数据源!$D$37+折现数据源!G37*折现数据源!$D$37+折现数据源!H37*折现数据源!$D$37+折现数据源!I37*折现数据源!$D$37+折现数据源!J37*折现数据源!$D$37+折现数据源!K37*折现数据源!$D$37+折现数据源!L37*折现数据源!$D$37+折现数据源!M37*折现数据源!$D$37+折现数据源!N37*折现数据源!$D$37+折现数据源!O37*折现数据源!$D$37+折现数据源!P37*折现数据源!$D$37+折现数据源!Q37*折现数据源!$D$37+折现数据源!R37*折现数据源!$D$37+折现数据源!S37*折现数据源!$D$37+折现数据源!T37*折现数据源!$D$37</f>
         <v/>
       </c>
       <c r="F38" s="29">
-        <f>SUMPRODUCT(折现数据源!U$4:U$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!V$4:V$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!W$4:W$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!X$4:X$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Y$4:Y$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Z$4:Z$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!AA$4:AA$67,折现数据源!$D$4:$D$67)</f>
+        <f>折现数据源!U37*折现数据源!$D$37+折现数据源!V37*折现数据源!$D$37+折现数据源!W37*折现数据源!$D$37+折现数据源!X37*折现数据源!$D$37+折现数据源!Y37*折现数据源!$D$37+折现数据源!Z37*折现数据源!$D$37+折现数据源!AA37*折现数据源!$D$37</f>
         <v/>
       </c>
       <c r="G38" s="31">
@@ -9745,11 +9745,11 @@
         <v/>
       </c>
       <c r="E39" s="29">
-        <f>SUMPRODUCT(折现数据源!E$4:E$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!F$4:F$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!G$4:G$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!H$4:H$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!I$4:I$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!J$4:J$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!K$4:K$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!L$4:L$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!M$4:M$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!N$4:N$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!O$4:O$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!P$4:P$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Q$4:Q$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!R$4:R$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!S$4:S$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!T$4:T$67,折现数据源!$D$4:$D$67)</f>
+        <f>折现数据源!E38*折现数据源!$D$38+折现数据源!F38*折现数据源!$D$38+折现数据源!G38*折现数据源!$D$38+折现数据源!H38*折现数据源!$D$38+折现数据源!I38*折现数据源!$D$38+折现数据源!J38*折现数据源!$D$38+折现数据源!K38*折现数据源!$D$38+折现数据源!L38*折现数据源!$D$38+折现数据源!M38*折现数据源!$D$38+折现数据源!N38*折现数据源!$D$38+折现数据源!O38*折现数据源!$D$38+折现数据源!P38*折现数据源!$D$38+折现数据源!Q38*折现数据源!$D$38+折现数据源!R38*折现数据源!$D$38+折现数据源!S38*折现数据源!$D$38+折现数据源!T38*折现数据源!$D$38</f>
         <v/>
       </c>
       <c r="F39" s="29">
-        <f>SUMPRODUCT(折现数据源!U$4:U$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!V$4:V$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!W$4:W$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!X$4:X$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Y$4:Y$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Z$4:Z$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!AA$4:AA$67,折现数据源!$D$4:$D$67)</f>
+        <f>折现数据源!U38*折现数据源!$D$38+折现数据源!V38*折现数据源!$D$38+折现数据源!W38*折现数据源!$D$38+折现数据源!X38*折现数据源!$D$38+折现数据源!Y38*折现数据源!$D$38+折现数据源!Z38*折现数据源!$D$38+折现数据源!AA38*折现数据源!$D$38</f>
         <v/>
       </c>
       <c r="G39" s="31">
@@ -9779,11 +9779,11 @@
         <v/>
       </c>
       <c r="E40" s="29">
-        <f>SUMPRODUCT(折现数据源!E$4:E$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!F$4:F$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!G$4:G$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!H$4:H$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!I$4:I$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!J$4:J$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!K$4:K$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!L$4:L$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!M$4:M$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!N$4:N$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!O$4:O$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!P$4:P$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Q$4:Q$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!R$4:R$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!S$4:S$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!T$4:T$67,折现数据源!$D$4:$D$67)</f>
+        <f>折现数据源!E39*折现数据源!$D$39+折现数据源!F39*折现数据源!$D$39+折现数据源!G39*折现数据源!$D$39+折现数据源!H39*折现数据源!$D$39+折现数据源!I39*折现数据源!$D$39+折现数据源!J39*折现数据源!$D$39+折现数据源!K39*折现数据源!$D$39+折现数据源!L39*折现数据源!$D$39+折现数据源!M39*折现数据源!$D$39+折现数据源!N39*折现数据源!$D$39+折现数据源!O39*折现数据源!$D$39+折现数据源!P39*折现数据源!$D$39+折现数据源!Q39*折现数据源!$D$39+折现数据源!R39*折现数据源!$D$39+折现数据源!S39*折现数据源!$D$39+折现数据源!T39*折现数据源!$D$39</f>
         <v/>
       </c>
       <c r="F40" s="29">
-        <f>SUMPRODUCT(折现数据源!U$4:U$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!V$4:V$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!W$4:W$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!X$4:X$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Y$4:Y$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Z$4:Z$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!AA$4:AA$67,折现数据源!$D$4:$D$67)</f>
+        <f>折现数据源!U39*折现数据源!$D$39+折现数据源!V39*折现数据源!$D$39+折现数据源!W39*折现数据源!$D$39+折现数据源!X39*折现数据源!$D$39+折现数据源!Y39*折现数据源!$D$39+折现数据源!Z39*折现数据源!$D$39+折现数据源!AA39*折现数据源!$D$39</f>
         <v/>
       </c>
       <c r="G40" s="31">
@@ -9813,11 +9813,11 @@
         <v/>
       </c>
       <c r="E41" s="29">
-        <f>SUMPRODUCT(折现数据源!E$4:E$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!F$4:F$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!G$4:G$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!H$4:H$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!I$4:I$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!J$4:J$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!K$4:K$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!L$4:L$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!M$4:M$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!N$4:N$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!O$4:O$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!P$4:P$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Q$4:Q$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!R$4:R$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!S$4:S$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!T$4:T$67,折现数据源!$D$4:$D$67)</f>
+        <f>折现数据源!E40*折现数据源!$D$40+折现数据源!F40*折现数据源!$D$40+折现数据源!G40*折现数据源!$D$40+折现数据源!H40*折现数据源!$D$40+折现数据源!I40*折现数据源!$D$40+折现数据源!J40*折现数据源!$D$40+折现数据源!K40*折现数据源!$D$40+折现数据源!L40*折现数据源!$D$40+折现数据源!M40*折现数据源!$D$40+折现数据源!N40*折现数据源!$D$40+折现数据源!O40*折现数据源!$D$40+折现数据源!P40*折现数据源!$D$40+折现数据源!Q40*折现数据源!$D$40+折现数据源!R40*折现数据源!$D$40+折现数据源!S40*折现数据源!$D$40+折现数据源!T40*折现数据源!$D$40</f>
         <v/>
       </c>
       <c r="F41" s="29">
-        <f>SUMPRODUCT(折现数据源!U$4:U$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!V$4:V$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!W$4:W$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!X$4:X$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Y$4:Y$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Z$4:Z$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!AA$4:AA$67,折现数据源!$D$4:$D$67)</f>
+        <f>折现数据源!U40*折现数据源!$D$40+折现数据源!V40*折现数据源!$D$40+折现数据源!W40*折现数据源!$D$40+折现数据源!X40*折现数据源!$D$40+折现数据源!Y40*折现数据源!$D$40+折现数据源!Z40*折现数据源!$D$40+折现数据源!AA40*折现数据源!$D$40</f>
         <v/>
       </c>
       <c r="G41" s="31">
@@ -9847,11 +9847,11 @@
         <v/>
       </c>
       <c r="E42" s="29">
-        <f>SUMPRODUCT(折现数据源!E$4:E$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!F$4:F$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!G$4:G$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!H$4:H$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!I$4:I$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!J$4:J$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!K$4:K$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!L$4:L$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!M$4:M$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!N$4:N$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!O$4:O$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!P$4:P$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Q$4:Q$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!R$4:R$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!S$4:S$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!T$4:T$67,折现数据源!$D$4:$D$67)</f>
+        <f>折现数据源!E41*折现数据源!$D$41+折现数据源!F41*折现数据源!$D$41+折现数据源!G41*折现数据源!$D$41+折现数据源!H41*折现数据源!$D$41+折现数据源!I41*折现数据源!$D$41+折现数据源!J41*折现数据源!$D$41+折现数据源!K41*折现数据源!$D$41+折现数据源!L41*折现数据源!$D$41+折现数据源!M41*折现数据源!$D$41+折现数据源!N41*折现数据源!$D$41+折现数据源!O41*折现数据源!$D$41+折现数据源!P41*折现数据源!$D$41+折现数据源!Q41*折现数据源!$D$41+折现数据源!R41*折现数据源!$D$41+折现数据源!S41*折现数据源!$D$41+折现数据源!T41*折现数据源!$D$41</f>
         <v/>
       </c>
       <c r="F42" s="29">
-        <f>SUMPRODUCT(折现数据源!U$4:U$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!V$4:V$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!W$4:W$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!X$4:X$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Y$4:Y$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Z$4:Z$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!AA$4:AA$67,折现数据源!$D$4:$D$67)</f>
+        <f>折现数据源!U41*折现数据源!$D$41+折现数据源!V41*折现数据源!$D$41+折现数据源!W41*折现数据源!$D$41+折现数据源!X41*折现数据源!$D$41+折现数据源!Y41*折现数据源!$D$41+折现数据源!Z41*折现数据源!$D$41+折现数据源!AA41*折现数据源!$D$41</f>
         <v/>
       </c>
       <c r="G42" s="31">
@@ -9881,11 +9881,11 @@
         <v/>
       </c>
       <c r="E43" s="29">
-        <f>SUMPRODUCT(折现数据源!E$4:E$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!F$4:F$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!G$4:G$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!H$4:H$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!I$4:I$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!J$4:J$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!K$4:K$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!L$4:L$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!M$4:M$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!N$4:N$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!O$4:O$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!P$4:P$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Q$4:Q$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!R$4:R$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!S$4:S$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!T$4:T$67,折现数据源!$D$4:$D$67)</f>
+        <f>折现数据源!E42*折现数据源!$D$42+折现数据源!F42*折现数据源!$D$42+折现数据源!G42*折现数据源!$D$42+折现数据源!H42*折现数据源!$D$42+折现数据源!I42*折现数据源!$D$42+折现数据源!J42*折现数据源!$D$42+折现数据源!K42*折现数据源!$D$42+折现数据源!L42*折现数据源!$D$42+折现数据源!M42*折现数据源!$D$42+折现数据源!N42*折现数据源!$D$42+折现数据源!O42*折现数据源!$D$42+折现数据源!P42*折现数据源!$D$42+折现数据源!Q42*折现数据源!$D$42+折现数据源!R42*折现数据源!$D$42+折现数据源!S42*折现数据源!$D$42+折现数据源!T42*折现数据源!$D$42</f>
         <v/>
       </c>
       <c r="F43" s="29">
-        <f>SUMPRODUCT(折现数据源!U$4:U$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!V$4:V$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!W$4:W$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!X$4:X$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Y$4:Y$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Z$4:Z$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!AA$4:AA$67,折现数据源!$D$4:$D$67)</f>
+        <f>折现数据源!U42*折现数据源!$D$42+折现数据源!V42*折现数据源!$D$42+折现数据源!W42*折现数据源!$D$42+折现数据源!X42*折现数据源!$D$42+折现数据源!Y42*折现数据源!$D$42+折现数据源!Z42*折现数据源!$D$42+折现数据源!AA42*折现数据源!$D$42</f>
         <v/>
       </c>
       <c r="G43" s="31">
@@ -9915,11 +9915,11 @@
         <v/>
       </c>
       <c r="E44" s="29">
-        <f>SUMPRODUCT(折现数据源!E$4:E$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!F$4:F$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!G$4:G$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!H$4:H$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!I$4:I$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!J$4:J$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!K$4:K$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!L$4:L$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!M$4:M$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!N$4:N$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!O$4:O$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!P$4:P$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Q$4:Q$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!R$4:R$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!S$4:S$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!T$4:T$67,折现数据源!$D$4:$D$67)</f>
+        <f>折现数据源!E43*折现数据源!$D$43+折现数据源!F43*折现数据源!$D$43+折现数据源!G43*折现数据源!$D$43+折现数据源!H43*折现数据源!$D$43+折现数据源!I43*折现数据源!$D$43+折现数据源!J43*折现数据源!$D$43+折现数据源!K43*折现数据源!$D$43+折现数据源!L43*折现数据源!$D$43+折现数据源!M43*折现数据源!$D$43+折现数据源!N43*折现数据源!$D$43+折现数据源!O43*折现数据源!$D$43+折现数据源!P43*折现数据源!$D$43+折现数据源!Q43*折现数据源!$D$43+折现数据源!R43*折现数据源!$D$43+折现数据源!S43*折现数据源!$D$43+折现数据源!T43*折现数据源!$D$43</f>
         <v/>
       </c>
       <c r="F44" s="29">
-        <f>SUMPRODUCT(折现数据源!U$4:U$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!V$4:V$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!W$4:W$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!X$4:X$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Y$4:Y$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Z$4:Z$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!AA$4:AA$67,折现数据源!$D$4:$D$67)</f>
+        <f>折现数据源!U43*折现数据源!$D$43+折现数据源!V43*折现数据源!$D$43+折现数据源!W43*折现数据源!$D$43+折现数据源!X43*折现数据源!$D$43+折现数据源!Y43*折现数据源!$D$43+折现数据源!Z43*折现数据源!$D$43+折现数据源!AA43*折现数据源!$D$43</f>
         <v/>
       </c>
       <c r="G44" s="31">
@@ -9949,11 +9949,11 @@
         <v/>
       </c>
       <c r="E45" s="29">
-        <f>SUMPRODUCT(折现数据源!E$4:E$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!F$4:F$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!G$4:G$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!H$4:H$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!I$4:I$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!J$4:J$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!K$4:K$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!L$4:L$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!M$4:M$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!N$4:N$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!O$4:O$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!P$4:P$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Q$4:Q$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!R$4:R$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!S$4:S$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!T$4:T$67,折现数据源!$D$4:$D$67)</f>
+        <f>折现数据源!E44*折现数据源!$D$44+折现数据源!F44*折现数据源!$D$44+折现数据源!G44*折现数据源!$D$44+折现数据源!H44*折现数据源!$D$44+折现数据源!I44*折现数据源!$D$44+折现数据源!J44*折现数据源!$D$44+折现数据源!K44*折现数据源!$D$44+折现数据源!L44*折现数据源!$D$44+折现数据源!M44*折现数据源!$D$44+折现数据源!N44*折现数据源!$D$44+折现数据源!O44*折现数据源!$D$44+折现数据源!P44*折现数据源!$D$44+折现数据源!Q44*折现数据源!$D$44+折现数据源!R44*折现数据源!$D$44+折现数据源!S44*折现数据源!$D$44+折现数据源!T44*折现数据源!$D$44</f>
         <v/>
       </c>
       <c r="F45" s="29">
-        <f>SUMPRODUCT(折现数据源!U$4:U$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!V$4:V$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!W$4:W$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!X$4:X$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Y$4:Y$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Z$4:Z$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!AA$4:AA$67,折现数据源!$D$4:$D$67)</f>
+        <f>折现数据源!U44*折现数据源!$D$44+折现数据源!V44*折现数据源!$D$44+折现数据源!W44*折现数据源!$D$44+折现数据源!X44*折现数据源!$D$44+折现数据源!Y44*折现数据源!$D$44+折现数据源!Z44*折现数据源!$D$44+折现数据源!AA44*折现数据源!$D$44</f>
         <v/>
       </c>
       <c r="G45" s="31">
@@ -9983,11 +9983,11 @@
         <v/>
       </c>
       <c r="E46" s="29">
-        <f>SUMPRODUCT(折现数据源!E$4:E$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!F$4:F$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!G$4:G$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!H$4:H$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!I$4:I$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!J$4:J$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!K$4:K$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!L$4:L$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!M$4:M$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!N$4:N$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!O$4:O$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!P$4:P$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Q$4:Q$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!R$4:R$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!S$4:S$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!T$4:T$67,折现数据源!$D$4:$D$67)</f>
+        <f>折现数据源!E45*折现数据源!$D$45+折现数据源!F45*折现数据源!$D$45+折现数据源!G45*折现数据源!$D$45+折现数据源!H45*折现数据源!$D$45+折现数据源!I45*折现数据源!$D$45+折现数据源!J45*折现数据源!$D$45+折现数据源!K45*折现数据源!$D$45+折现数据源!L45*折现数据源!$D$45+折现数据源!M45*折现数据源!$D$45+折现数据源!N45*折现数据源!$D$45+折现数据源!O45*折现数据源!$D$45+折现数据源!P45*折现数据源!$D$45+折现数据源!Q45*折现数据源!$D$45+折现数据源!R45*折现数据源!$D$45+折现数据源!S45*折现数据源!$D$45+折现数据源!T45*折现数据源!$D$45</f>
         <v/>
       </c>
       <c r="F46" s="29">
-        <f>SUMPRODUCT(折现数据源!U$4:U$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!V$4:V$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!W$4:W$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!X$4:X$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Y$4:Y$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Z$4:Z$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!AA$4:AA$67,折现数据源!$D$4:$D$67)</f>
+        <f>折现数据源!U45*折现数据源!$D$45+折现数据源!V45*折现数据源!$D$45+折现数据源!W45*折现数据源!$D$45+折现数据源!X45*折现数据源!$D$45+折现数据源!Y45*折现数据源!$D$45+折现数据源!Z45*折现数据源!$D$45+折现数据源!AA45*折现数据源!$D$45</f>
         <v/>
       </c>
       <c r="G46" s="31">
@@ -10017,11 +10017,11 @@
         <v/>
       </c>
       <c r="E47" s="29">
-        <f>SUMPRODUCT(折现数据源!E$4:E$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!F$4:F$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!G$4:G$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!H$4:H$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!I$4:I$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!J$4:J$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!K$4:K$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!L$4:L$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!M$4:M$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!N$4:N$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!O$4:O$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!P$4:P$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Q$4:Q$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!R$4:R$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!S$4:S$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!T$4:T$67,折现数据源!$D$4:$D$67)</f>
+        <f>折现数据源!E46*折现数据源!$D$46+折现数据源!F46*折现数据源!$D$46+折现数据源!G46*折现数据源!$D$46+折现数据源!H46*折现数据源!$D$46+折现数据源!I46*折现数据源!$D$46+折现数据源!J46*折现数据源!$D$46+折现数据源!K46*折现数据源!$D$46+折现数据源!L46*折现数据源!$D$46+折现数据源!M46*折现数据源!$D$46+折现数据源!N46*折现数据源!$D$46+折现数据源!O46*折现数据源!$D$46+折现数据源!P46*折现数据源!$D$46+折现数据源!Q46*折现数据源!$D$46+折现数据源!R46*折现数据源!$D$46+折现数据源!S46*折现数据源!$D$46+折现数据源!T46*折现数据源!$D$46</f>
         <v/>
       </c>
       <c r="F47" s="29">
-        <f>SUMPRODUCT(折现数据源!U$4:U$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!V$4:V$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!W$4:W$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!X$4:X$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Y$4:Y$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Z$4:Z$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!AA$4:AA$67,折现数据源!$D$4:$D$67)</f>
+        <f>折现数据源!U46*折现数据源!$D$46+折现数据源!V46*折现数据源!$D$46+折现数据源!W46*折现数据源!$D$46+折现数据源!X46*折现数据源!$D$46+折现数据源!Y46*折现数据源!$D$46+折现数据源!Z46*折现数据源!$D$46+折现数据源!AA46*折现数据源!$D$46</f>
         <v/>
       </c>
       <c r="G47" s="31">
@@ -10051,11 +10051,11 @@
         <v/>
       </c>
       <c r="E48" s="29">
-        <f>SUMPRODUCT(折现数据源!E$4:E$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!F$4:F$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!G$4:G$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!H$4:H$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!I$4:I$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!J$4:J$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!K$4:K$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!L$4:L$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!M$4:M$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!N$4:N$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!O$4:O$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!P$4:P$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Q$4:Q$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!R$4:R$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!S$4:S$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!T$4:T$67,折现数据源!$D$4:$D$67)</f>
+        <f>折现数据源!E47*折现数据源!$D$47+折现数据源!F47*折现数据源!$D$47+折现数据源!G47*折现数据源!$D$47+折现数据源!H47*折现数据源!$D$47+折现数据源!I47*折现数据源!$D$47+折现数据源!J47*折现数据源!$D$47+折现数据源!K47*折现数据源!$D$47+折现数据源!L47*折现数据源!$D$47+折现数据源!M47*折现数据源!$D$47+折现数据源!N47*折现数据源!$D$47+折现数据源!O47*折现数据源!$D$47+折现数据源!P47*折现数据源!$D$47+折现数据源!Q47*折现数据源!$D$47+折现数据源!R47*折现数据源!$D$47+折现数据源!S47*折现数据源!$D$47+折现数据源!T47*折现数据源!$D$47</f>
         <v/>
       </c>
       <c r="F48" s="29">
-        <f>SUMPRODUCT(折现数据源!U$4:U$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!V$4:V$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!W$4:W$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!X$4:X$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Y$4:Y$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Z$4:Z$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!AA$4:AA$67,折现数据源!$D$4:$D$67)</f>
+        <f>折现数据源!U47*折现数据源!$D$47+折现数据源!V47*折现数据源!$D$47+折现数据源!W47*折现数据源!$D$47+折现数据源!X47*折现数据源!$D$47+折现数据源!Y47*折现数据源!$D$47+折现数据源!Z47*折现数据源!$D$47+折现数据源!AA47*折现数据源!$D$47</f>
         <v/>
       </c>
       <c r="G48" s="31">
@@ -10085,11 +10085,11 @@
         <v/>
       </c>
       <c r="E49" s="29">
-        <f>SUMPRODUCT(折现数据源!E$4:E$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!F$4:F$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!G$4:G$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!H$4:H$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!I$4:I$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!J$4:J$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!K$4:K$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!L$4:L$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!M$4:M$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!N$4:N$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!O$4:O$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!P$4:P$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Q$4:Q$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!R$4:R$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!S$4:S$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!T$4:T$67,折现数据源!$D$4:$D$67)</f>
+        <f>折现数据源!E48*折现数据源!$D$48+折现数据源!F48*折现数据源!$D$48+折现数据源!G48*折现数据源!$D$48+折现数据源!H48*折现数据源!$D$48+折现数据源!I48*折现数据源!$D$48+折现数据源!J48*折现数据源!$D$48+折现数据源!K48*折现数据源!$D$48+折现数据源!L48*折现数据源!$D$48+折现数据源!M48*折现数据源!$D$48+折现数据源!N48*折现数据源!$D$48+折现数据源!O48*折现数据源!$D$48+折现数据源!P48*折现数据源!$D$48+折现数据源!Q48*折现数据源!$D$48+折现数据源!R48*折现数据源!$D$48+折现数据源!S48*折现数据源!$D$48+折现数据源!T48*折现数据源!$D$48</f>
         <v/>
       </c>
       <c r="F49" s="29">
-        <f>SUMPRODUCT(折现数据源!U$4:U$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!V$4:V$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!W$4:W$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!X$4:X$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Y$4:Y$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Z$4:Z$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!AA$4:AA$67,折现数据源!$D$4:$D$67)</f>
+        <f>折现数据源!U48*折现数据源!$D$48+折现数据源!V48*折现数据源!$D$48+折现数据源!W48*折现数据源!$D$48+折现数据源!X48*折现数据源!$D$48+折现数据源!Y48*折现数据源!$D$48+折现数据源!Z48*折现数据源!$D$48+折现数据源!AA48*折现数据源!$D$48</f>
         <v/>
       </c>
       <c r="G49" s="31">
@@ -10119,11 +10119,11 @@
         <v/>
       </c>
       <c r="E50" s="29">
-        <f>SUMPRODUCT(折现数据源!E$4:E$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!F$4:F$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!G$4:G$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!H$4:H$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!I$4:I$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!J$4:J$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!K$4:K$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!L$4:L$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!M$4:M$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!N$4:N$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!O$4:O$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!P$4:P$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Q$4:Q$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!R$4:R$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!S$4:S$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!T$4:T$67,折现数据源!$D$4:$D$67)</f>
+        <f>折现数据源!E49*折现数据源!$D$49+折现数据源!F49*折现数据源!$D$49+折现数据源!G49*折现数据源!$D$49+折现数据源!H49*折现数据源!$D$49+折现数据源!I49*折现数据源!$D$49+折现数据源!J49*折现数据源!$D$49+折现数据源!K49*折现数据源!$D$49+折现数据源!L49*折现数据源!$D$49+折现数据源!M49*折现数据源!$D$49+折现数据源!N49*折现数据源!$D$49+折现数据源!O49*折现数据源!$D$49+折现数据源!P49*折现数据源!$D$49+折现数据源!Q49*折现数据源!$D$49+折现数据源!R49*折现数据源!$D$49+折现数据源!S49*折现数据源!$D$49+折现数据源!T49*折现数据源!$D$49</f>
         <v/>
       </c>
       <c r="F50" s="29">
-        <f>SUMPRODUCT(折现数据源!U$4:U$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!V$4:V$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!W$4:W$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!X$4:X$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Y$4:Y$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Z$4:Z$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!AA$4:AA$67,折现数据源!$D$4:$D$67)</f>
+        <f>折现数据源!U49*折现数据源!$D$49+折现数据源!V49*折现数据源!$D$49+折现数据源!W49*折现数据源!$D$49+折现数据源!X49*折现数据源!$D$49+折现数据源!Y49*折现数据源!$D$49+折现数据源!Z49*折现数据源!$D$49+折现数据源!AA49*折现数据源!$D$49</f>
         <v/>
       </c>
       <c r="G50" s="31">
@@ -10153,11 +10153,11 @@
         <v/>
       </c>
       <c r="E51" s="29">
-        <f>SUMPRODUCT(折现数据源!E$4:E$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!F$4:F$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!G$4:G$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!H$4:H$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!I$4:I$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!J$4:J$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!K$4:K$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!L$4:L$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!M$4:M$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!N$4:N$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!O$4:O$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!P$4:P$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Q$4:Q$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!R$4:R$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!S$4:S$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!T$4:T$67,折现数据源!$D$4:$D$67)</f>
+        <f>折现数据源!E50*折现数据源!$D$50+折现数据源!F50*折现数据源!$D$50+折现数据源!G50*折现数据源!$D$50+折现数据源!H50*折现数据源!$D$50+折现数据源!I50*折现数据源!$D$50+折现数据源!J50*折现数据源!$D$50+折现数据源!K50*折现数据源!$D$50+折现数据源!L50*折现数据源!$D$50+折现数据源!M50*折现数据源!$D$50+折现数据源!N50*折现数据源!$D$50+折现数据源!O50*折现数据源!$D$50+折现数据源!P50*折现数据源!$D$50+折现数据源!Q50*折现数据源!$D$50+折现数据源!R50*折现数据源!$D$50+折现数据源!S50*折现数据源!$D$50+折现数据源!T50*折现数据源!$D$50</f>
         <v/>
       </c>
       <c r="F51" s="29">
-        <f>SUMPRODUCT(折现数据源!U$4:U$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!V$4:V$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!W$4:W$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!X$4:X$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Y$4:Y$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Z$4:Z$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!AA$4:AA$67,折现数据源!$D$4:$D$67)</f>
+        <f>折现数据源!U50*折现数据源!$D$50+折现数据源!V50*折现数据源!$D$50+折现数据源!W50*折现数据源!$D$50+折现数据源!X50*折现数据源!$D$50+折现数据源!Y50*折现数据源!$D$50+折现数据源!Z50*折现数据源!$D$50+折现数据源!AA50*折现数据源!$D$50</f>
         <v/>
       </c>
       <c r="G51" s="31">
@@ -10187,11 +10187,11 @@
         <v/>
       </c>
       <c r="E52" s="29">
-        <f>SUMPRODUCT(折现数据源!E$4:E$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!F$4:F$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!G$4:G$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!H$4:H$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!I$4:I$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!J$4:J$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!K$4:K$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!L$4:L$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!M$4:M$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!N$4:N$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!O$4:O$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!P$4:P$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Q$4:Q$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!R$4:R$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!S$4:S$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!T$4:T$67,折现数据源!$D$4:$D$67)</f>
+        <f>折现数据源!E51*折现数据源!$D$51+折现数据源!F51*折现数据源!$D$51+折现数据源!G51*折现数据源!$D$51+折现数据源!H51*折现数据源!$D$51+折现数据源!I51*折现数据源!$D$51+折现数据源!J51*折现数据源!$D$51+折现数据源!K51*折现数据源!$D$51+折现数据源!L51*折现数据源!$D$51+折现数据源!M51*折现数据源!$D$51+折现数据源!N51*折现数据源!$D$51+折现数据源!O51*折现数据源!$D$51+折现数据源!P51*折现数据源!$D$51+折现数据源!Q51*折现数据源!$D$51+折现数据源!R51*折现数据源!$D$51+折现数据源!S51*折现数据源!$D$51+折现数据源!T51*折现数据源!$D$51</f>
         <v/>
       </c>
       <c r="F52" s="29">
-        <f>SUMPRODUCT(折现数据源!U$4:U$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!V$4:V$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!W$4:W$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!X$4:X$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Y$4:Y$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Z$4:Z$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!AA$4:AA$67,折现数据源!$D$4:$D$67)</f>
+        <f>折现数据源!U51*折现数据源!$D$51+折现数据源!V51*折现数据源!$D$51+折现数据源!W51*折现数据源!$D$51+折现数据源!X51*折现数据源!$D$51+折现数据源!Y51*折现数据源!$D$51+折现数据源!Z51*折现数据源!$D$51+折现数据源!AA51*折现数据源!$D$51</f>
         <v/>
       </c>
       <c r="G52" s="31">
@@ -10221,11 +10221,11 @@
         <v/>
       </c>
       <c r="E53" s="29">
-        <f>SUMPRODUCT(折现数据源!E$4:E$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!F$4:F$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!G$4:G$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!H$4:H$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!I$4:I$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!J$4:J$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!K$4:K$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!L$4:L$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!M$4:M$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!N$4:N$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!O$4:O$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!P$4:P$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Q$4:Q$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!R$4:R$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!S$4:S$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!T$4:T$67,折现数据源!$D$4:$D$67)</f>
+        <f>折现数据源!E52*折现数据源!$D$52+折现数据源!F52*折现数据源!$D$52+折现数据源!G52*折现数据源!$D$52+折现数据源!H52*折现数据源!$D$52+折现数据源!I52*折现数据源!$D$52+折现数据源!J52*折现数据源!$D$52+折现数据源!K52*折现数据源!$D$52+折现数据源!L52*折现数据源!$D$52+折现数据源!M52*折现数据源!$D$52+折现数据源!N52*折现数据源!$D$52+折现数据源!O52*折现数据源!$D$52+折现数据源!P52*折现数据源!$D$52+折现数据源!Q52*折现数据源!$D$52+折现数据源!R52*折现数据源!$D$52+折现数据源!S52*折现数据源!$D$52+折现数据源!T52*折现数据源!$D$52</f>
         <v/>
       </c>
       <c r="F53" s="29">
-        <f>SUMPRODUCT(折现数据源!U$4:U$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!V$4:V$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!W$4:W$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!X$4:X$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Y$4:Y$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Z$4:Z$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!AA$4:AA$67,折现数据源!$D$4:$D$67)</f>
+        <f>折现数据源!U52*折现数据源!$D$52+折现数据源!V52*折现数据源!$D$52+折现数据源!W52*折现数据源!$D$52+折现数据源!X52*折现数据源!$D$52+折现数据源!Y52*折现数据源!$D$52+折现数据源!Z52*折现数据源!$D$52+折现数据源!AA52*折现数据源!$D$52</f>
         <v/>
       </c>
       <c r="G53" s="31">
@@ -10255,11 +10255,11 @@
         <v/>
       </c>
       <c r="E54" s="29">
-        <f>SUMPRODUCT(折现数据源!E$4:E$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!F$4:F$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!G$4:G$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!H$4:H$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!I$4:I$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!J$4:J$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!K$4:K$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!L$4:L$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!M$4:M$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!N$4:N$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!O$4:O$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!P$4:P$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Q$4:Q$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!R$4:R$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!S$4:S$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!T$4:T$67,折现数据源!$D$4:$D$67)</f>
+        <f>折现数据源!E53*折现数据源!$D$53+折现数据源!F53*折现数据源!$D$53+折现数据源!G53*折现数据源!$D$53+折现数据源!H53*折现数据源!$D$53+折现数据源!I53*折现数据源!$D$53+折现数据源!J53*折现数据源!$D$53+折现数据源!K53*折现数据源!$D$53+折现数据源!L53*折现数据源!$D$53+折现数据源!M53*折现数据源!$D$53+折现数据源!N53*折现数据源!$D$53+折现数据源!O53*折现数据源!$D$53+折现数据源!P53*折现数据源!$D$53+折现数据源!Q53*折现数据源!$D$53+折现数据源!R53*折现数据源!$D$53+折现数据源!S53*折现数据源!$D$53+折现数据源!T53*折现数据源!$D$53</f>
         <v/>
       </c>
       <c r="F54" s="29">
-        <f>SUMPRODUCT(折现数据源!U$4:U$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!V$4:V$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!W$4:W$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!X$4:X$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Y$4:Y$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Z$4:Z$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!AA$4:AA$67,折现数据源!$D$4:$D$67)</f>
+        <f>折现数据源!U53*折现数据源!$D$53+折现数据源!V53*折现数据源!$D$53+折现数据源!W53*折现数据源!$D$53+折现数据源!X53*折现数据源!$D$53+折现数据源!Y53*折现数据源!$D$53+折现数据源!Z53*折现数据源!$D$53+折现数据源!AA53*折现数据源!$D$53</f>
         <v/>
       </c>
       <c r="G54" s="31">
@@ -10289,11 +10289,11 @@
         <v/>
       </c>
       <c r="E55" s="29">
-        <f>SUMPRODUCT(折现数据源!E$4:E$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!F$4:F$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!G$4:G$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!H$4:H$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!I$4:I$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!J$4:J$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!K$4:K$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!L$4:L$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!M$4:M$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!N$4:N$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!O$4:O$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!P$4:P$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Q$4:Q$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!R$4:R$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!S$4:S$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!T$4:T$67,折现数据源!$D$4:$D$67)</f>
+        <f>折现数据源!E54*折现数据源!$D$54+折现数据源!F54*折现数据源!$D$54+折现数据源!G54*折现数据源!$D$54+折现数据源!H54*折现数据源!$D$54+折现数据源!I54*折现数据源!$D$54+折现数据源!J54*折现数据源!$D$54+折现数据源!K54*折现数据源!$D$54+折现数据源!L54*折现数据源!$D$54+折现数据源!M54*折现数据源!$D$54+折现数据源!N54*折现数据源!$D$54+折现数据源!O54*折现数据源!$D$54+折现数据源!P54*折现数据源!$D$54+折现数据源!Q54*折现数据源!$D$54+折现数据源!R54*折现数据源!$D$54+折现数据源!S54*折现数据源!$D$54+折现数据源!T54*折现数据源!$D$54</f>
         <v/>
       </c>
       <c r="F55" s="29">
-        <f>SUMPRODUCT(折现数据源!U$4:U$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!V$4:V$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!W$4:W$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!X$4:X$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Y$4:Y$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Z$4:Z$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!AA$4:AA$67,折现数据源!$D$4:$D$67)</f>
+        <f>折现数据源!U54*折现数据源!$D$54+折现数据源!V54*折现数据源!$D$54+折现数据源!W54*折现数据源!$D$54+折现数据源!X54*折现数据源!$D$54+折现数据源!Y54*折现数据源!$D$54+折现数据源!Z54*折现数据源!$D$54+折现数据源!AA54*折现数据源!$D$54</f>
         <v/>
       </c>
       <c r="G55" s="31">
@@ -10323,11 +10323,11 @@
         <v/>
       </c>
       <c r="E56" s="29">
-        <f>SUMPRODUCT(折现数据源!E$4:E$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!F$4:F$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!G$4:G$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!H$4:H$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!I$4:I$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!J$4:J$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!K$4:K$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!L$4:L$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!M$4:M$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!N$4:N$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!O$4:O$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!P$4:P$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Q$4:Q$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!R$4:R$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!S$4:S$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!T$4:T$67,折现数据源!$D$4:$D$67)</f>
+        <f>折现数据源!E55*折现数据源!$D$55+折现数据源!F55*折现数据源!$D$55+折现数据源!G55*折现数据源!$D$55+折现数据源!H55*折现数据源!$D$55+折现数据源!I55*折现数据源!$D$55+折现数据源!J55*折现数据源!$D$55+折现数据源!K55*折现数据源!$D$55+折现数据源!L55*折现数据源!$D$55+折现数据源!M55*折现数据源!$D$55+折现数据源!N55*折现数据源!$D$55+折现数据源!O55*折现数据源!$D$55+折现数据源!P55*折现数据源!$D$55+折现数据源!Q55*折现数据源!$D$55+折现数据源!R55*折现数据源!$D$55+折现数据源!S55*折现数据源!$D$55+折现数据源!T55*折现数据源!$D$55</f>
         <v/>
       </c>
       <c r="F56" s="29">
-        <f>SUMPRODUCT(折现数据源!U$4:U$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!V$4:V$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!W$4:W$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!X$4:X$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Y$4:Y$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Z$4:Z$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!AA$4:AA$67,折现数据源!$D$4:$D$67)</f>
+        <f>折现数据源!U55*折现数据源!$D$55+折现数据源!V55*折现数据源!$D$55+折现数据源!W55*折现数据源!$D$55+折现数据源!X55*折现数据源!$D$55+折现数据源!Y55*折现数据源!$D$55+折现数据源!Z55*折现数据源!$D$55+折现数据源!AA55*折现数据源!$D$55</f>
         <v/>
       </c>
       <c r="G56" s="31">
@@ -10357,11 +10357,11 @@
         <v/>
       </c>
       <c r="E57" s="29">
-        <f>SUMPRODUCT(折现数据源!E$4:E$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!F$4:F$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!G$4:G$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!H$4:H$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!I$4:I$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!J$4:J$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!K$4:K$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!L$4:L$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!M$4:M$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!N$4:N$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!O$4:O$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!P$4:P$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Q$4:Q$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!R$4:R$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!S$4:S$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!T$4:T$67,折现数据源!$D$4:$D$67)</f>
+        <f>折现数据源!E56*折现数据源!$D$56+折现数据源!F56*折现数据源!$D$56+折现数据源!G56*折现数据源!$D$56+折现数据源!H56*折现数据源!$D$56+折现数据源!I56*折现数据源!$D$56+折现数据源!J56*折现数据源!$D$56+折现数据源!K56*折现数据源!$D$56+折现数据源!L56*折现数据源!$D$56+折现数据源!M56*折现数据源!$D$56+折现数据源!N56*折现数据源!$D$56+折现数据源!O56*折现数据源!$D$56+折现数据源!P56*折现数据源!$D$56+折现数据源!Q56*折现数据源!$D$56+折现数据源!R56*折现数据源!$D$56+折现数据源!S56*折现数据源!$D$56+折现数据源!T56*折现数据源!$D$56</f>
         <v/>
       </c>
       <c r="F57" s="29">
-        <f>SUMPRODUCT(折现数据源!U$4:U$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!V$4:V$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!W$4:W$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!X$4:X$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Y$4:Y$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Z$4:Z$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!AA$4:AA$67,折现数据源!$D$4:$D$67)</f>
+        <f>折现数据源!U56*折现数据源!$D$56+折现数据源!V56*折现数据源!$D$56+折现数据源!W56*折现数据源!$D$56+折现数据源!X56*折现数据源!$D$56+折现数据源!Y56*折现数据源!$D$56+折现数据源!Z56*折现数据源!$D$56+折现数据源!AA56*折现数据源!$D$56</f>
         <v/>
       </c>
       <c r="G57" s="31">
@@ -10391,11 +10391,11 @@
         <v/>
       </c>
       <c r="E58" s="29">
-        <f>SUMPRODUCT(折现数据源!E$4:E$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!F$4:F$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!G$4:G$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!H$4:H$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!I$4:I$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!J$4:J$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!K$4:K$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!L$4:L$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!M$4:M$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!N$4:N$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!O$4:O$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!P$4:P$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Q$4:Q$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!R$4:R$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!S$4:S$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!T$4:T$67,折现数据源!$D$4:$D$67)</f>
+        <f>折现数据源!E57*折现数据源!$D$57+折现数据源!F57*折现数据源!$D$57+折现数据源!G57*折现数据源!$D$57+折现数据源!H57*折现数据源!$D$57+折现数据源!I57*折现数据源!$D$57+折现数据源!J57*折现数据源!$D$57+折现数据源!K57*折现数据源!$D$57+折现数据源!L57*折现数据源!$D$57+折现数据源!M57*折现数据源!$D$57+折现数据源!N57*折现数据源!$D$57+折现数据源!O57*折现数据源!$D$57+折现数据源!P57*折现数据源!$D$57+折现数据源!Q57*折现数据源!$D$57+折现数据源!R57*折现数据源!$D$57+折现数据源!S57*折现数据源!$D$57+折现数据源!T57*折现数据源!$D$57</f>
         <v/>
       </c>
       <c r="F58" s="29">
-        <f>SUMPRODUCT(折现数据源!U$4:U$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!V$4:V$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!W$4:W$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!X$4:X$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Y$4:Y$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Z$4:Z$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!AA$4:AA$67,折现数据源!$D$4:$D$67)</f>
+        <f>折现数据源!U57*折现数据源!$D$57+折现数据源!V57*折现数据源!$D$57+折现数据源!W57*折现数据源!$D$57+折现数据源!X57*折现数据源!$D$57+折现数据源!Y57*折现数据源!$D$57+折现数据源!Z57*折现数据源!$D$57+折现数据源!AA57*折现数据源!$D$57</f>
         <v/>
       </c>
       <c r="G58" s="31">
@@ -10425,11 +10425,11 @@
         <v/>
       </c>
       <c r="E59" s="29">
-        <f>SUMPRODUCT(折现数据源!E$4:E$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!F$4:F$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!G$4:G$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!H$4:H$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!I$4:I$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!J$4:J$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!K$4:K$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!L$4:L$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!M$4:M$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!N$4:N$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!O$4:O$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!P$4:P$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Q$4:Q$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!R$4:R$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!S$4:S$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!T$4:T$67,折现数据源!$D$4:$D$67)</f>
+        <f>折现数据源!E58*折现数据源!$D$58+折现数据源!F58*折现数据源!$D$58+折现数据源!G58*折现数据源!$D$58+折现数据源!H58*折现数据源!$D$58+折现数据源!I58*折现数据源!$D$58+折现数据源!J58*折现数据源!$D$58+折现数据源!K58*折现数据源!$D$58+折现数据源!L58*折现数据源!$D$58+折现数据源!M58*折现数据源!$D$58+折现数据源!N58*折现数据源!$D$58+折现数据源!O58*折现数据源!$D$58+折现数据源!P58*折现数据源!$D$58+折现数据源!Q58*折现数据源!$D$58+折现数据源!R58*折现数据源!$D$58+折现数据源!S58*折现数据源!$D$58+折现数据源!T58*折现数据源!$D$58</f>
         <v/>
       </c>
       <c r="F59" s="29">
-        <f>SUMPRODUCT(折现数据源!U$4:U$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!V$4:V$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!W$4:W$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!X$4:X$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Y$4:Y$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Z$4:Z$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!AA$4:AA$67,折现数据源!$D$4:$D$67)</f>
+        <f>折现数据源!U58*折现数据源!$D$58+折现数据源!V58*折现数据源!$D$58+折现数据源!W58*折现数据源!$D$58+折现数据源!X58*折现数据源!$D$58+折现数据源!Y58*折现数据源!$D$58+折现数据源!Z58*折现数据源!$D$58+折现数据源!AA58*折现数据源!$D$58</f>
         <v/>
       </c>
       <c r="G59" s="31">
@@ -10459,11 +10459,11 @@
         <v/>
       </c>
       <c r="E60" s="29">
-        <f>SUMPRODUCT(折现数据源!E$4:E$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!F$4:F$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!G$4:G$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!H$4:H$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!I$4:I$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!J$4:J$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!K$4:K$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!L$4:L$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!M$4:M$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!N$4:N$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!O$4:O$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!P$4:P$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Q$4:Q$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!R$4:R$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!S$4:S$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!T$4:T$67,折现数据源!$D$4:$D$67)</f>
+        <f>折现数据源!E59*折现数据源!$D$59+折现数据源!F59*折现数据源!$D$59+折现数据源!G59*折现数据源!$D$59+折现数据源!H59*折现数据源!$D$59+折现数据源!I59*折现数据源!$D$59+折现数据源!J59*折现数据源!$D$59+折现数据源!K59*折现数据源!$D$59+折现数据源!L59*折现数据源!$D$59+折现数据源!M59*折现数据源!$D$59+折现数据源!N59*折现数据源!$D$59+折现数据源!O59*折现数据源!$D$59+折现数据源!P59*折现数据源!$D$59+折现数据源!Q59*折现数据源!$D$59+折现数据源!R59*折现数据源!$D$59+折现数据源!S59*折现数据源!$D$59+折现数据源!T59*折现数据源!$D$59</f>
         <v/>
       </c>
       <c r="F60" s="29">
-        <f>SUMPRODUCT(折现数据源!U$4:U$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!V$4:V$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!W$4:W$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!X$4:X$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Y$4:Y$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Z$4:Z$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!AA$4:AA$67,折现数据源!$D$4:$D$67)</f>
+        <f>折现数据源!U59*折现数据源!$D$59+折现数据源!V59*折现数据源!$D$59+折现数据源!W59*折现数据源!$D$59+折现数据源!X59*折现数据源!$D$59+折现数据源!Y59*折现数据源!$D$59+折现数据源!Z59*折现数据源!$D$59+折现数据源!AA59*折现数据源!$D$59</f>
         <v/>
       </c>
       <c r="G60" s="31">
@@ -10493,11 +10493,11 @@
         <v/>
       </c>
       <c r="E61" s="29">
-        <f>SUMPRODUCT(折现数据源!E$4:E$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!F$4:F$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!G$4:G$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!H$4:H$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!I$4:I$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!J$4:J$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!K$4:K$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!L$4:L$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!M$4:M$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!N$4:N$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!O$4:O$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!P$4:P$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Q$4:Q$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!R$4:R$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!S$4:S$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!T$4:T$67,折现数据源!$D$4:$D$67)</f>
+        <f>折现数据源!E60*折现数据源!$D$60+折现数据源!F60*折现数据源!$D$60+折现数据源!G60*折现数据源!$D$60+折现数据源!H60*折现数据源!$D$60+折现数据源!I60*折现数据源!$D$60+折现数据源!J60*折现数据源!$D$60+折现数据源!K60*折现数据源!$D$60+折现数据源!L60*折现数据源!$D$60+折现数据源!M60*折现数据源!$D$60+折现数据源!N60*折现数据源!$D$60+折现数据源!O60*折现数据源!$D$60+折现数据源!P60*折现数据源!$D$60+折现数据源!Q60*折现数据源!$D$60+折现数据源!R60*折现数据源!$D$60+折现数据源!S60*折现数据源!$D$60+折现数据源!T60*折现数据源!$D$60</f>
         <v/>
       </c>
       <c r="F61" s="29">
-        <f>SUMPRODUCT(折现数据源!U$4:U$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!V$4:V$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!W$4:W$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!X$4:X$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Y$4:Y$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Z$4:Z$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!AA$4:AA$67,折现数据源!$D$4:$D$67)</f>
+        <f>折现数据源!U60*折现数据源!$D$60+折现数据源!V60*折现数据源!$D$60+折现数据源!W60*折现数据源!$D$60+折现数据源!X60*折现数据源!$D$60+折现数据源!Y60*折现数据源!$D$60+折现数据源!Z60*折现数据源!$D$60+折现数据源!AA60*折现数据源!$D$60</f>
         <v/>
       </c>
       <c r="G61" s="31">
@@ -10527,11 +10527,11 @@
         <v/>
       </c>
       <c r="E62" s="29">
-        <f>SUMPRODUCT(折现数据源!E$4:E$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!F$4:F$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!G$4:G$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!H$4:H$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!I$4:I$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!J$4:J$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!K$4:K$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!L$4:L$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!M$4:M$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!N$4:N$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!O$4:O$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!P$4:P$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Q$4:Q$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!R$4:R$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!S$4:S$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!T$4:T$67,折现数据源!$D$4:$D$67)</f>
+        <f>折现数据源!E61*折现数据源!$D$61+折现数据源!F61*折现数据源!$D$61+折现数据源!G61*折现数据源!$D$61+折现数据源!H61*折现数据源!$D$61+折现数据源!I61*折现数据源!$D$61+折现数据源!J61*折现数据源!$D$61+折现数据源!K61*折现数据源!$D$61+折现数据源!L61*折现数据源!$D$61+折现数据源!M61*折现数据源!$D$61+折现数据源!N61*折现数据源!$D$61+折现数据源!O61*折现数据源!$D$61+折现数据源!P61*折现数据源!$D$61+折现数据源!Q61*折现数据源!$D$61+折现数据源!R61*折现数据源!$D$61+折现数据源!S61*折现数据源!$D$61+折现数据源!T61*折现数据源!$D$61</f>
         <v/>
       </c>
       <c r="F62" s="29">
-        <f>SUMPRODUCT(折现数据源!U$4:U$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!V$4:V$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!W$4:W$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!X$4:X$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Y$4:Y$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Z$4:Z$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!AA$4:AA$67,折现数据源!$D$4:$D$67)</f>
+        <f>折现数据源!U61*折现数据源!$D$61+折现数据源!V61*折现数据源!$D$61+折现数据源!W61*折现数据源!$D$61+折现数据源!X61*折现数据源!$D$61+折现数据源!Y61*折现数据源!$D$61+折现数据源!Z61*折现数据源!$D$61+折现数据源!AA61*折现数据源!$D$61</f>
         <v/>
       </c>
       <c r="G62" s="31">
@@ -10561,11 +10561,11 @@
         <v/>
       </c>
       <c r="E63" s="29">
-        <f>SUMPRODUCT(折现数据源!E$4:E$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!F$4:F$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!G$4:G$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!H$4:H$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!I$4:I$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!J$4:J$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!K$4:K$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!L$4:L$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!M$4:M$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!N$4:N$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!O$4:O$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!P$4:P$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Q$4:Q$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!R$4:R$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!S$4:S$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!T$4:T$67,折现数据源!$D$4:$D$67)</f>
+        <f>折现数据源!E62*折现数据源!$D$62+折现数据源!F62*折现数据源!$D$62+折现数据源!G62*折现数据源!$D$62+折现数据源!H62*折现数据源!$D$62+折现数据源!I62*折现数据源!$D$62+折现数据源!J62*折现数据源!$D$62+折现数据源!K62*折现数据源!$D$62+折现数据源!L62*折现数据源!$D$62+折现数据源!M62*折现数据源!$D$62+折现数据源!N62*折现数据源!$D$62+折现数据源!O62*折现数据源!$D$62+折现数据源!P62*折现数据源!$D$62+折现数据源!Q62*折现数据源!$D$62+折现数据源!R62*折现数据源!$D$62+折现数据源!S62*折现数据源!$D$62+折现数据源!T62*折现数据源!$D$62</f>
         <v/>
       </c>
       <c r="F63" s="29">
-        <f>SUMPRODUCT(折现数据源!U$4:U$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!V$4:V$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!W$4:W$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!X$4:X$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Y$4:Y$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Z$4:Z$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!AA$4:AA$67,折现数据源!$D$4:$D$67)</f>
+        <f>折现数据源!U62*折现数据源!$D$62+折现数据源!V62*折现数据源!$D$62+折现数据源!W62*折现数据源!$D$62+折现数据源!X62*折现数据源!$D$62+折现数据源!Y62*折现数据源!$D$62+折现数据源!Z62*折现数据源!$D$62+折现数据源!AA62*折现数据源!$D$62</f>
         <v/>
       </c>
       <c r="G63" s="31">
@@ -10595,11 +10595,11 @@
         <v/>
       </c>
       <c r="E64" s="29">
-        <f>SUMPRODUCT(折现数据源!E$4:E$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!F$4:F$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!G$4:G$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!H$4:H$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!I$4:I$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!J$4:J$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!K$4:K$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!L$4:L$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!M$4:M$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!N$4:N$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!O$4:O$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!P$4:P$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Q$4:Q$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!R$4:R$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!S$4:S$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!T$4:T$67,折现数据源!$D$4:$D$67)</f>
+        <f>折现数据源!E63*折现数据源!$D$63+折现数据源!F63*折现数据源!$D$63+折现数据源!G63*折现数据源!$D$63+折现数据源!H63*折现数据源!$D$63+折现数据源!I63*折现数据源!$D$63+折现数据源!J63*折现数据源!$D$63+折现数据源!K63*折现数据源!$D$63+折现数据源!L63*折现数据源!$D$63+折现数据源!M63*折现数据源!$D$63+折现数据源!N63*折现数据源!$D$63+折现数据源!O63*折现数据源!$D$63+折现数据源!P63*折现数据源!$D$63+折现数据源!Q63*折现数据源!$D$63+折现数据源!R63*折现数据源!$D$63+折现数据源!S63*折现数据源!$D$63+折现数据源!T63*折现数据源!$D$63</f>
         <v/>
       </c>
       <c r="F64" s="29">
-        <f>SUMPRODUCT(折现数据源!U$4:U$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!V$4:V$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!W$4:W$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!X$4:X$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Y$4:Y$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Z$4:Z$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!AA$4:AA$67,折现数据源!$D$4:$D$67)</f>
+        <f>折现数据源!U63*折现数据源!$D$63+折现数据源!V63*折现数据源!$D$63+折现数据源!W63*折现数据源!$D$63+折现数据源!X63*折现数据源!$D$63+折现数据源!Y63*折现数据源!$D$63+折现数据源!Z63*折现数据源!$D$63+折现数据源!AA63*折现数据源!$D$63</f>
         <v/>
       </c>
       <c r="G64" s="31">
@@ -10629,11 +10629,11 @@
         <v/>
       </c>
       <c r="E65" s="29">
-        <f>SUMPRODUCT(折现数据源!E$4:E$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!F$4:F$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!G$4:G$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!H$4:H$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!I$4:I$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!J$4:J$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!K$4:K$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!L$4:L$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!M$4:M$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!N$4:N$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!O$4:O$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!P$4:P$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Q$4:Q$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!R$4:R$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!S$4:S$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!T$4:T$67,折现数据源!$D$4:$D$67)</f>
+        <f>折现数据源!E64*折现数据源!$D$64+折现数据源!F64*折现数据源!$D$64+折现数据源!G64*折现数据源!$D$64+折现数据源!H64*折现数据源!$D$64+折现数据源!I64*折现数据源!$D$64+折现数据源!J64*折现数据源!$D$64+折现数据源!K64*折现数据源!$D$64+折现数据源!L64*折现数据源!$D$64+折现数据源!M64*折现数据源!$D$64+折现数据源!N64*折现数据源!$D$64+折现数据源!O64*折现数据源!$D$64+折现数据源!P64*折现数据源!$D$64+折现数据源!Q64*折现数据源!$D$64+折现数据源!R64*折现数据源!$D$64+折现数据源!S64*折现数据源!$D$64+折现数据源!T64*折现数据源!$D$64</f>
         <v/>
       </c>
       <c r="F65" s="29">
-        <f>SUMPRODUCT(折现数据源!U$4:U$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!V$4:V$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!W$4:W$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!X$4:X$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Y$4:Y$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Z$4:Z$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!AA$4:AA$67,折现数据源!$D$4:$D$67)</f>
+        <f>折现数据源!U64*折现数据源!$D$64+折现数据源!V64*折现数据源!$D$64+折现数据源!W64*折现数据源!$D$64+折现数据源!X64*折现数据源!$D$64+折现数据源!Y64*折现数据源!$D$64+折现数据源!Z64*折现数据源!$D$64+折现数据源!AA64*折现数据源!$D$64</f>
         <v/>
       </c>
       <c r="G65" s="31">
@@ -10663,11 +10663,11 @@
         <v/>
       </c>
       <c r="E66" s="29">
-        <f>SUMPRODUCT(折现数据源!E$4:E$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!F$4:F$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!G$4:G$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!H$4:H$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!I$4:I$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!J$4:J$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!K$4:K$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!L$4:L$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!M$4:M$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!N$4:N$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!O$4:O$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!P$4:P$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Q$4:Q$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!R$4:R$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!S$4:S$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!T$4:T$67,折现数据源!$D$4:$D$67)</f>
+        <f>折现数据源!E65*折现数据源!$D$65+折现数据源!F65*折现数据源!$D$65+折现数据源!G65*折现数据源!$D$65+折现数据源!H65*折现数据源!$D$65+折现数据源!I65*折现数据源!$D$65+折现数据源!J65*折现数据源!$D$65+折现数据源!K65*折现数据源!$D$65+折现数据源!L65*折现数据源!$D$65+折现数据源!M65*折现数据源!$D$65+折现数据源!N65*折现数据源!$D$65+折现数据源!O65*折现数据源!$D$65+折现数据源!P65*折现数据源!$D$65+折现数据源!Q65*折现数据源!$D$65+折现数据源!R65*折现数据源!$D$65+折现数据源!S65*折现数据源!$D$65+折现数据源!T65*折现数据源!$D$65</f>
         <v/>
       </c>
       <c r="F66" s="29">
-        <f>SUMPRODUCT(折现数据源!U$4:U$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!V$4:V$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!W$4:W$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!X$4:X$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Y$4:Y$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Z$4:Z$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!AA$4:AA$67,折现数据源!$D$4:$D$67)</f>
+        <f>折现数据源!U65*折现数据源!$D$65+折现数据源!V65*折现数据源!$D$65+折现数据源!W65*折现数据源!$D$65+折现数据源!X65*折现数据源!$D$65+折现数据源!Y65*折现数据源!$D$65+折现数据源!Z65*折现数据源!$D$65+折现数据源!AA65*折现数据源!$D$65</f>
         <v/>
       </c>
       <c r="G66" s="31">
@@ -10697,11 +10697,11 @@
         <v/>
       </c>
       <c r="E67" s="29">
-        <f>SUMPRODUCT(折现数据源!E$4:E$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!F$4:F$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!G$4:G$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!H$4:H$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!I$4:I$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!J$4:J$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!K$4:K$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!L$4:L$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!M$4:M$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!N$4:N$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!O$4:O$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!P$4:P$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Q$4:Q$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!R$4:R$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!S$4:S$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!T$4:T$67,折现数据源!$D$4:$D$67)</f>
+        <f>折现数据源!E66*折现数据源!$D$66+折现数据源!F66*折现数据源!$D$66+折现数据源!G66*折现数据源!$D$66+折现数据源!H66*折现数据源!$D$66+折现数据源!I66*折现数据源!$D$66+折现数据源!J66*折现数据源!$D$66+折现数据源!K66*折现数据源!$D$66+折现数据源!L66*折现数据源!$D$66+折现数据源!M66*折现数据源!$D$66+折现数据源!N66*折现数据源!$D$66+折现数据源!O66*折现数据源!$D$66+折现数据源!P66*折现数据源!$D$66+折现数据源!Q66*折现数据源!$D$66+折现数据源!R66*折现数据源!$D$66+折现数据源!S66*折现数据源!$D$66+折现数据源!T66*折现数据源!$D$66</f>
         <v/>
       </c>
       <c r="F67" s="29">
-        <f>SUMPRODUCT(折现数据源!U$4:U$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!V$4:V$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!W$4:W$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!X$4:X$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Y$4:Y$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Z$4:Z$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!AA$4:AA$67,折现数据源!$D$4:$D$67)</f>
+        <f>折现数据源!U66*折现数据源!$D$66+折现数据源!V66*折现数据源!$D$66+折现数据源!W66*折现数据源!$D$66+折现数据源!X66*折现数据源!$D$66+折现数据源!Y66*折现数据源!$D$66+折现数据源!Z66*折现数据源!$D$66+折现数据源!AA66*折现数据源!$D$66</f>
         <v/>
       </c>
       <c r="G67" s="31">
@@ -10731,11 +10731,11 @@
         <v/>
       </c>
       <c r="E68" s="29">
-        <f>SUMPRODUCT(折现数据源!E$4:E$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!F$4:F$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!G$4:G$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!H$4:H$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!I$4:I$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!J$4:J$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!K$4:K$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!L$4:L$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!M$4:M$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!N$4:N$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!O$4:O$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!P$4:P$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Q$4:Q$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!R$4:R$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!S$4:S$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!T$4:T$67,折现数据源!$D$4:$D$67)</f>
+        <f>折现数据源!E67*折现数据源!$D$67+折现数据源!F67*折现数据源!$D$67+折现数据源!G67*折现数据源!$D$67+折现数据源!H67*折现数据源!$D$67+折现数据源!I67*折现数据源!$D$67+折现数据源!J67*折现数据源!$D$67+折现数据源!K67*折现数据源!$D$67+折现数据源!L67*折现数据源!$D$67+折现数据源!M67*折现数据源!$D$67+折现数据源!N67*折现数据源!$D$67+折现数据源!O67*折现数据源!$D$67+折现数据源!P67*折现数据源!$D$67+折现数据源!Q67*折现数据源!$D$67+折现数据源!R67*折现数据源!$D$67+折现数据源!S67*折现数据源!$D$67+折现数据源!T67*折现数据源!$D$67</f>
         <v/>
       </c>
       <c r="F68" s="29">
-        <f>SUMPRODUCT(折现数据源!U$4:U$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!V$4:V$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!W$4:W$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!X$4:X$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Y$4:Y$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!Z$4:Z$67,折现数据源!$D$4:$D$67)+SUMPRODUCT(折现数据源!AA$4:AA$67,折现数据源!$D$4:$D$67)</f>
+        <f>折现数据源!U67*折现数据源!$D$67+折现数据源!V67*折现数据源!$D$67+折现数据源!W67*折现数据源!$D$67+折现数据源!X67*折现数据源!$D$67+折现数据源!Y67*折现数据源!$D$67+折现数据源!Z67*折现数据源!$D$67+折现数据源!AA67*折现数据源!$D$67</f>
         <v/>
       </c>
       <c r="G68" s="31">
